--- a/school_timetable.xlsx
+++ b/school_timetable.xlsx
@@ -760,8 +760,10 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -922,8 +924,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="n">
-        <v>2</v>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -1084,8 +1088,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="n">
-        <v>3</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -1246,8 +1252,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr"/>
-      <c r="B5" s="2" t="n">
-        <v>4</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -1408,8 +1416,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="n">
-        <v>5</v>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -1626,8 +1636,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="n">
-        <v>6</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -1788,8 +1800,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="n">
-        <v>7</v>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -1950,8 +1964,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="n">
-        <v>8</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -2116,8 +2132,10 @@
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>1</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -2278,8 +2296,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="n">
-        <v>2</v>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -2440,8 +2460,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="n">
-        <v>3</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -2602,8 +2624,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="n">
-        <v>4</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -2764,8 +2788,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="n">
-        <v>5</v>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -2982,8 +3008,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="n">
-        <v>6</v>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -3144,8 +3172,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="n">
-        <v>7</v>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -3306,8 +3336,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="n">
-        <v>8</v>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -3472,8 +3504,10 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
-        <v>1</v>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -3634,8 +3668,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="n">
-        <v>2</v>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -3796,8 +3832,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="n">
-        <v>3</v>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -3958,8 +3996,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="2" t="n">
-        <v>4</v>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -4120,8 +4160,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="n">
-        <v>5</v>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -4338,8 +4380,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="n">
-        <v>6</v>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -4500,8 +4544,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr"/>
-      <c r="B27" s="2" t="n">
-        <v>7</v>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -4662,8 +4708,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="2" t="n">
-        <v>8</v>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -4828,8 +4876,10 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
-        <v>1</v>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -4990,8 +5040,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="2" t="n">
-        <v>2</v>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -5152,8 +5204,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr"/>
-      <c r="B31" s="2" t="n">
-        <v>3</v>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -5314,8 +5368,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="n">
-        <v>4</v>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -5476,8 +5532,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="n">
-        <v>5</v>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
@@ -5694,8 +5752,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="2" t="n">
-        <v>6</v>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -5856,8 +5916,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="n">
-        <v>7</v>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -6018,8 +6080,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="2" t="n">
-        <v>8</v>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
@@ -6184,8 +6248,10 @@
           <t>Friday</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
-        <v>1</v>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -6346,8 +6412,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="n">
-        <v>2</v>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -6508,8 +6576,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="n">
-        <v>3</v>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -6670,8 +6740,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="2" t="n">
-        <v>4</v>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -6888,8 +6960,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="n">
-        <v>5</v>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
@@ -7050,8 +7124,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="n">
-        <v>6</v>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>

--- a/school_timetable.xlsx
+++ b/school_timetable.xlsx
@@ -833,11 +833,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>7D COMPUTER</t>
-        </is>
-      </c>
+      <c r="S2" s="2" t="inlineStr"/>
       <c r="T2" s="2" t="inlineStr">
         <is>
           <t>9E COMPUTER IX-X</t>
@@ -845,7 +841,11 @@
       </c>
       <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>7D ISLAMIAT</t>
+        </is>
+      </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
           <t>7B SINDHI</t>
@@ -1010,7 +1010,11 @@
       </c>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>8B GP</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>8A MATHS</t>
@@ -1074,11 +1078,7 @@
       </c>
       <c r="AT3" s="2" t="inlineStr"/>
       <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr">
-        <is>
-          <t>8B GAMES</t>
-        </is>
-      </c>
+      <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" s="2" t="inlineStr"/>
       <c r="AX3" s="2" t="inlineStr">
         <is>
@@ -1167,11 +1167,7 @@
           <t>9E COMPUTER IX-X</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>8B S.ST</t>
-        </is>
-      </c>
+      <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
@@ -1618,11 +1614,7 @@
           <t>10C CHEMISTRY</t>
         </is>
       </c>
-      <c r="AR7" s="2" t="inlineStr">
-        <is>
-          <t>6B HISTORY</t>
-        </is>
-      </c>
+      <c r="AR7" s="2" t="inlineStr"/>
       <c r="AS7" s="2" t="inlineStr"/>
       <c r="AT7" s="2" t="inlineStr"/>
       <c r="AU7" s="2" t="inlineStr"/>
@@ -1786,12 +1778,12 @@
           <t xml:space="preserve">9F GENERAL SCIENCE </t>
         </is>
       </c>
-      <c r="AR8" s="2" t="inlineStr"/>
-      <c r="AS8" s="2" t="inlineStr">
-        <is>
-          <t>7D SINDHI</t>
-        </is>
-      </c>
+      <c r="AR8" s="2" t="inlineStr">
+        <is>
+          <t>7D S.ST</t>
+        </is>
+      </c>
+      <c r="AS8" s="2" t="inlineStr"/>
       <c r="AT8" s="2" t="inlineStr"/>
       <c r="AU8" s="2" t="inlineStr"/>
       <c r="AV8" s="2" t="inlineStr"/>
@@ -2177,7 +2169,11 @@
           <t>7A GENERAL SCIENCE</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>8B URDU</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>8C GENERAL SCIENCE</t>
@@ -2215,11 +2211,7 @@
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr"/>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>8B S.ST</t>
-        </is>
-      </c>
+      <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
           <t>9E ENGLISH</t>
@@ -3312,11 +3304,7 @@
           <t>9B CHEMISTRY</t>
         </is>
       </c>
-      <c r="AP18" s="2" t="inlineStr">
-        <is>
-          <t>8B MATHS</t>
-        </is>
-      </c>
+      <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr">
         <is>
@@ -3326,7 +3314,11 @@
       <c r="AS18" s="2" t="inlineStr"/>
       <c r="AT18" s="2" t="inlineStr"/>
       <c r="AU18" s="2" t="inlineStr"/>
-      <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AV18" s="2" t="inlineStr">
+        <is>
+          <t>8B GAMES</t>
+        </is>
+      </c>
       <c r="AW18" s="2" t="inlineStr">
         <is>
           <t>7B GAMES</t>
@@ -3369,11 +3361,7 @@
           <t>7D GENERAL SCIENCE</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>8B URDU</t>
-        </is>
-      </c>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
@@ -3476,7 +3464,11 @@
           <t>9D CHEMISTRY</t>
         </is>
       </c>
-      <c r="AP19" s="2" t="inlineStr"/>
+      <c r="AP19" s="2" t="inlineStr">
+        <is>
+          <t>8B MATHS</t>
+        </is>
+      </c>
       <c r="AQ19" s="2" t="inlineStr">
         <is>
           <t>10B CHEMISTRY</t>
@@ -3753,11 +3745,7 @@
           <t>9F ISLAMIAT IX</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>8B ARABIC</t>
-        </is>
-      </c>
+      <c r="AA21" s="2" t="inlineStr"/>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>10D SINDHI-X</t>
@@ -3780,7 +3768,11 @@
         </is>
       </c>
       <c r="AG21" s="2" t="inlineStr"/>
-      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr">
+        <is>
+          <t>8B ISLAMIAT</t>
+        </is>
+      </c>
       <c r="AI21" s="2" t="inlineStr">
         <is>
           <t>10E LIBRARY</t>
@@ -3903,7 +3895,11 @@
           <t>7B COMPUTER</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>8B S.ST</t>
+        </is>
+      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
           <t>7A ENGLISH</t>
@@ -3944,11 +3940,7 @@
           <t>10F PAKISTAN STUDIES</t>
         </is>
       </c>
-      <c r="AH22" s="2" t="inlineStr">
-        <is>
-          <t>8B ISLAMIAT</t>
-        </is>
-      </c>
+      <c r="AH22" s="2" t="inlineStr"/>
       <c r="AI22" s="2" t="inlineStr"/>
       <c r="AJ22" s="2" t="inlineStr"/>
       <c r="AK22" s="2" t="inlineStr">
@@ -3986,13 +3978,13 @@
       </c>
       <c r="AT22" s="2" t="inlineStr"/>
       <c r="AU22" s="2" t="inlineStr"/>
-      <c r="AV22" s="2" t="inlineStr">
-        <is>
-          <t>8A GAMES</t>
-        </is>
-      </c>
+      <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" s="2" t="inlineStr"/>
-      <c r="AX22" s="2" t="inlineStr"/>
+      <c r="AX22" s="2" t="inlineStr">
+        <is>
+          <t>8A AI</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr"/>
@@ -4236,7 +4228,11 @@
           <t>9F MATHS</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6C S.ST</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>7E GENERAL SCIENCE</t>
@@ -4278,7 +4274,11 @@
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr"/>
-      <c r="T25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>8B COMPUTER</t>
+        </is>
+      </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
           <t>10E ENGLISH</t>
@@ -4297,16 +4297,8 @@
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr"/>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>6C ISLAMIAT</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>8B SINDHI</t>
-        </is>
-      </c>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
           <t>9A MATHS</t>
@@ -4429,7 +4421,11 @@
           <t>6E ENGLISH</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>7D MATHS</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
           <t>6C MATHS</t>
@@ -4443,7 +4439,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7D COMPUTER</t>
+          <t>8A COMPUTER</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr"/>
@@ -4486,11 +4482,7 @@
           <t>9D MATHS</t>
         </is>
       </c>
-      <c r="AF26" s="2" t="inlineStr">
-        <is>
-          <t>8A GEOGRAPHY</t>
-        </is>
-      </c>
+      <c r="AF26" s="2" t="inlineStr"/>
       <c r="AG26" s="2" t="inlineStr">
         <is>
           <t>8C S.ST</t>
@@ -4609,7 +4601,11 @@
           <t>9F COMPUTER IX-X</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>7D COMPUTER</t>
+        </is>
+      </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
           <t>10F COMPUTER IX-X</t>
@@ -4617,11 +4613,7 @@
       </c>
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr"/>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>7D ISLAMIAT</t>
-        </is>
-      </c>
+      <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
           <t>10A SINDHI-X</t>
@@ -4750,11 +4742,7 @@
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>6A MATHS</t>
-        </is>
-      </c>
+      <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>7E URDU</t>
@@ -4800,7 +4788,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>8B GP</t>
+          <t>8B SINDHI</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr"/>
@@ -4868,7 +4856,11 @@
       <c r="AU28" s="2" t="inlineStr"/>
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" s="2" t="inlineStr"/>
-      <c r="AX28" s="2" t="inlineStr"/>
+      <c r="AX28" s="2" t="inlineStr">
+        <is>
+          <t>6A AI</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5081,7 +5073,11 @@
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>6E MATHS</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
@@ -5179,11 +5175,7 @@
         </is>
       </c>
       <c r="AR30" s="2" t="inlineStr"/>
-      <c r="AS30" s="2" t="inlineStr">
-        <is>
-          <t>6E SINDHI</t>
-        </is>
-      </c>
+      <c r="AS30" s="2" t="inlineStr"/>
       <c r="AT30" s="2" t="inlineStr"/>
       <c r="AU30" s="2" t="inlineStr"/>
       <c r="AV30" s="2" t="inlineStr">
@@ -5265,11 +5257,7 @@
           <t>7A COMPUTER</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>8A COMPUTER</t>
-        </is>
-      </c>
+      <c r="S31" s="2" t="inlineStr"/>
       <c r="T31" s="2" t="inlineStr">
         <is>
           <t>7C COMPUTER</t>
@@ -5314,7 +5302,11 @@
           <t>10F MATHS</t>
         </is>
       </c>
-      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr">
+        <is>
+          <t>8A GEOGRAPHY</t>
+        </is>
+      </c>
       <c r="AG31" s="2" t="inlineStr"/>
       <c r="AH31" s="2" t="inlineStr">
         <is>
@@ -5417,7 +5409,11 @@
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>7A MATHS</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
           <t>6B MATHS</t>
@@ -5510,25 +5506,21 @@
       </c>
       <c r="AP32" s="2" t="inlineStr"/>
       <c r="AQ32" s="2" t="inlineStr"/>
-      <c r="AR32" s="2" t="inlineStr">
-        <is>
-          <t>7A HISTORY</t>
-        </is>
-      </c>
+      <c r="AR32" s="2" t="inlineStr"/>
       <c r="AS32" s="2" t="inlineStr"/>
       <c r="AT32" s="2" t="inlineStr"/>
       <c r="AU32" s="2" t="inlineStr"/>
-      <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AV32" s="2" t="inlineStr">
+        <is>
+          <t>8A GAMES</t>
+        </is>
+      </c>
       <c r="AW32" s="2" t="inlineStr">
         <is>
           <t>6A GAMES</t>
         </is>
       </c>
-      <c r="AX32" s="2" t="inlineStr">
-        <is>
-          <t>8A AI</t>
-        </is>
-      </c>
+      <c r="AX32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr"/>
@@ -5726,11 +5718,7 @@
           <t xml:space="preserve">9F GENERAL SCIENCE </t>
         </is>
       </c>
-      <c r="AR34" s="2" t="inlineStr">
-        <is>
-          <t>6E S.ST</t>
-        </is>
-      </c>
+      <c r="AR34" s="2" t="inlineStr"/>
       <c r="AS34" s="2" t="inlineStr"/>
       <c r="AT34" s="2" t="inlineStr"/>
       <c r="AU34" s="2" t="inlineStr"/>
@@ -5797,11 +5785,7 @@
           <t>6E ENGLISH</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>7D MATHS</t>
-        </is>
-      </c>
+      <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
           <t>6C MATHS</t>
@@ -5817,12 +5801,12 @@
           <t>8D COMPUTER</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr"/>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>8B COMPUTER</t>
-        </is>
-      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>7D COMPUTER</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr"/>
       <c r="U35" s="2" t="inlineStr">
         <is>
           <t>10E ENGLISH</t>
@@ -5931,11 +5915,7 @@
           <t>10C ENGLISH</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>6D MATHS</t>
-        </is>
-      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>10D PAKISTAN STUDIES</t>
@@ -5977,11 +5957,7 @@
           <t>7B S.ST</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>7D MATHS</t>
-        </is>
-      </c>
+      <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr">
         <is>
@@ -6071,11 +6047,19 @@
       <c r="AP36" s="2" t="inlineStr"/>
       <c r="AQ36" s="2" t="inlineStr"/>
       <c r="AR36" s="2" t="inlineStr"/>
-      <c r="AS36" s="2" t="inlineStr"/>
+      <c r="AS36" s="2" t="inlineStr">
+        <is>
+          <t>7D SINDHI</t>
+        </is>
+      </c>
       <c r="AT36" s="2" t="inlineStr"/>
       <c r="AU36" s="2" t="inlineStr"/>
       <c r="AV36" s="2" t="inlineStr"/>
-      <c r="AW36" s="2" t="inlineStr"/>
+      <c r="AW36" s="2" t="inlineStr">
+        <is>
+          <t>6D GAMES</t>
+        </is>
+      </c>
       <c r="AX36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
@@ -6259,18 +6243,18 @@
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>6D MATHS</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>6C GENERAL SCIENCE</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>6D URDU</t>
-        </is>
-      </c>
+      <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
@@ -6438,7 +6422,11 @@
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>6D URDU</t>
+        </is>
+      </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
           <t>6C ENGLISH</t>
@@ -6461,11 +6449,7 @@
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>6E MATHS</t>
-        </is>
-      </c>
+      <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
           <t>9C MATHS</t>
@@ -6559,15 +6543,15 @@
           <t>7D S.ST</t>
         </is>
       </c>
-      <c r="AS39" s="2" t="inlineStr"/>
+      <c r="AS39" s="2" t="inlineStr">
+        <is>
+          <t>6E SINDHI</t>
+        </is>
+      </c>
       <c r="AT39" s="2" t="inlineStr"/>
       <c r="AU39" s="2" t="inlineStr"/>
       <c r="AV39" s="2" t="inlineStr"/>
-      <c r="AW39" s="2" t="inlineStr">
-        <is>
-          <t>6D GAMES</t>
-        </is>
-      </c>
+      <c r="AW39" s="2" t="inlineStr"/>
       <c r="AX39" s="2" t="inlineStr">
         <is>
           <t>6B AI</t>
@@ -6882,7 +6866,11 @@
           <t>10B CHEMISTRY</t>
         </is>
       </c>
-      <c r="AR41" s="2" t="inlineStr"/>
+      <c r="AR41" s="2" t="inlineStr">
+        <is>
+          <t>6E S.ST</t>
+        </is>
+      </c>
       <c r="AS41" s="2" t="inlineStr">
         <is>
           <t>7E SINDHI</t>
@@ -6895,11 +6883,7 @@
           <t>10F GAMES</t>
         </is>
       </c>
-      <c r="AW41" s="2" t="inlineStr">
-        <is>
-          <t>6E GAMES</t>
-        </is>
-      </c>
+      <c r="AW41" s="2" t="inlineStr"/>
       <c r="AX41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
@@ -6976,11 +6960,7 @@
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>6C S.ST</t>
-        </is>
-      </c>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t>7E GENERAL SCIENCE</t>
@@ -7023,10 +7003,14 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7A MATHS</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr"/>
+          <t>7D MATHS</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>6C MATHS</t>
+        </is>
+      </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>9A URDU</t>
@@ -7112,7 +7096,7 @@
       <c r="AQ43" s="2" t="inlineStr"/>
       <c r="AR43" s="2" t="inlineStr">
         <is>
-          <t>7D S.ST</t>
+          <t>7A HISTORY</t>
         </is>
       </c>
       <c r="AS43" s="2" t="inlineStr"/>
@@ -7192,7 +7176,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6C MATHS</t>
+          <t>6A MATHS</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -7225,7 +7209,11 @@
       <c r="X44" s="2" t="inlineStr"/>
       <c r="Y44" s="2" t="inlineStr"/>
       <c r="Z44" s="2" t="inlineStr"/>
-      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>6C ISLAMIAT</t>
+        </is>
+      </c>
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr"/>
@@ -7280,11 +7268,7 @@
       <c r="AU44" s="2" t="inlineStr"/>
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" s="2" t="inlineStr"/>
-      <c r="AX44" s="2" t="inlineStr">
-        <is>
-          <t>6A AI</t>
-        </is>
-      </c>
+      <c r="AX44" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/school_timetable.xlsx
+++ b/school_timetable.xlsx
@@ -498,7 +498,7 @@
     <col width="17" customWidth="1" min="40" max="40"/>
     <col width="17" customWidth="1" min="41" max="41"/>
     <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="23" customWidth="1" min="43" max="43"/>
+    <col width="22" customWidth="1" min="43" max="43"/>
     <col width="19" customWidth="1" min="44" max="44"/>
     <col width="13" customWidth="1" min="45" max="45"/>
     <col width="18" customWidth="1" min="46" max="46"/>
@@ -839,11 +839,7 @@
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>9C COMPUTER IX-X</t>
-        </is>
-      </c>
+      <c r="S2" s="2" t="inlineStr"/>
       <c r="T2" s="2" t="inlineStr">
         <is>
           <t>7C COMPUTER</t>
@@ -882,7 +878,11 @@
           <t>9F ECONOMICS</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="inlineStr"/>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>9C ISLAMIAT IX</t>
+        </is>
+      </c>
       <c r="AI2" s="2" t="inlineStr"/>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>7B ENGLISH</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>6B GENERAL SCIENCE</t>
@@ -970,16 +974,8 @@
           <t>8D URDU</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>7B S.ST</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>7D MATHS</t>
-        </is>
-      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr">
@@ -989,7 +985,7 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>10E COMPUTER IX-X</t>
+          <t>9C COMPUTER IX-X</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
@@ -1027,7 +1023,11 @@
           <t>9A ISLAMIAT IX</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>7C ISLAMIAT</t>
+        </is>
+      </c>
       <c r="AB3" s="3" t="inlineStr"/>
       <c r="AC3" s="3" t="inlineStr"/>
       <c r="AD3" s="3" t="inlineStr">
@@ -1042,13 +1042,17 @@
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr">
-        <is>
-          <t>9C ISLAMIAT IX</t>
-        </is>
-      </c>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>9B LIBRARY</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>10E PHYSICS</t>
+        </is>
+      </c>
       <c r="AK3" s="3" t="inlineStr">
         <is>
           <t>9D ENGLISH</t>
@@ -1060,11 +1064,7 @@
           <t>10B PHYSICS</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>9B BIOLOGY</t>
-        </is>
-      </c>
+      <c r="AN3" s="3" t="inlineStr"/>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>9E CHEMISTRY</t>
@@ -1072,7 +1072,11 @@
       </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>7D S.ST</t>
+        </is>
+      </c>
       <c r="AS3" s="3" t="inlineStr"/>
       <c r="AT3" s="3" t="inlineStr"/>
       <c r="AU3" s="3" t="inlineStr"/>
@@ -1081,11 +1085,7 @@
           <t>8A GAMES</t>
         </is>
       </c>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>7C GAMES</t>
-        </is>
-      </c>
+      <c r="AW3" s="3" t="inlineStr"/>
       <c r="AX3" s="3" t="inlineStr">
         <is>
           <t>7A AI</t>
@@ -1137,11 +1137,7 @@
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9E URDU</t>
-        </is>
-      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr">
@@ -1171,9 +1167,17 @@
           <t>8B ENGLISH</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>7D ISLAMIAT</t>
+        </is>
+      </c>
       <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>6E ARABIC</t>
+        </is>
+      </c>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="inlineStr">
         <is>
@@ -1213,11 +1217,7 @@
       </c>
       <c r="AI4" s="2" t="inlineStr"/>
       <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr">
-        <is>
-          <t>7C S.ST</t>
-        </is>
-      </c>
+      <c r="AK4" s="2" t="inlineStr"/>
       <c r="AL4" s="2" t="inlineStr">
         <is>
           <t>10B BIOLOGY</t>
@@ -1229,18 +1229,18 @@
           <t>10A CHEMISTRY</t>
         </is>
       </c>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>9E CHEMISTRY</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9F GENERAL SCIENCE </t>
-        </is>
-      </c>
-      <c r="AR4" s="2" t="inlineStr">
-        <is>
-          <t>7D S.ST</t>
-        </is>
-      </c>
+          <t>9F GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AR4" s="2" t="inlineStr"/>
       <c r="AS4" s="2" t="inlineStr">
         <is>
           <t>6D SINDHI</t>
@@ -1251,7 +1251,7 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" s="2" t="inlineStr">
         <is>
-          <t>6E GAMES</t>
+          <t>7C GAMES</t>
         </is>
       </c>
       <c r="AX4" s="2" t="inlineStr"/>
@@ -1525,7 +1525,11 @@
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>9E URDU</t>
+        </is>
+      </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>8C ENGLISH</t>
@@ -1548,11 +1552,7 @@
           <t>7D COMPUTER</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>9E COMPUTER IX-X</t>
-        </is>
-      </c>
+      <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr">
         <is>
           <t>10B ENGLISH</t>
@@ -1629,14 +1629,14 @@
           <t>6B HISTORY</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>8D SINDHI</t>
+        </is>
+      </c>
       <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>8D GAMES</t>
-        </is>
-      </c>
+      <c r="AV7" s="3" t="inlineStr"/>
       <c r="AW7" s="3" t="inlineStr"/>
       <c r="AX7" s="3" t="inlineStr"/>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>8A COMPUTER</t>
+          <t>10E COMPUTER IX-X</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1916,7 +1916,11 @@
         </is>
       </c>
       <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>8A GEOGRAPHY</t>
+        </is>
+      </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
           <t>8D S.ST</t>
@@ -1927,11 +1931,7 @@
           <t>7E PH</t>
         </is>
       </c>
-      <c r="AI9" s="3" t="inlineStr">
-        <is>
-          <t>10E LIBRARY</t>
-        </is>
-      </c>
+      <c r="AI9" s="3" t="inlineStr"/>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
           <t>9E PHYSICS</t>
@@ -1939,11 +1939,7 @@
       </c>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr">
-        <is>
-          <t>9A PHYSICS</t>
-        </is>
-      </c>
+      <c r="AM9" s="3" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
       <c r="AP9" s="3" t="inlineStr">
@@ -1962,7 +1958,7 @@
       <c r="AU9" s="3" t="inlineStr"/>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>9B GAMES</t>
+          <t>9A GAMES</t>
         </is>
       </c>
       <c r="AW9" s="3" t="inlineStr"/>
@@ -2001,11 +1997,7 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7B ENGLISH</t>
-        </is>
-      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -2019,7 +2011,11 @@
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>6E TS</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
@@ -2029,7 +2025,7 @@
       <c r="R10" s="2" t="inlineStr"/>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6E COMPUTER</t>
+          <t>10E COMPUTER IX-X</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -2053,7 +2049,11 @@
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr"/>
-      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>7B ISLAMIAT</t>
+        </is>
+      </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>6D ISLAMIAT</t>
@@ -2088,11 +2088,7 @@
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr"/>
       <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr">
-        <is>
-          <t>10E PHYSICS</t>
-        </is>
-      </c>
+      <c r="AJ10" s="2" t="inlineStr"/>
       <c r="AK10" s="2" t="inlineStr">
         <is>
           <t>10D ENGLISH</t>
@@ -2397,7 +2393,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>7C ISLAMIAT</t>
+          <t>7C ARABIC</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr"/>
@@ -2507,11 +2503,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>6E TS</t>
-        </is>
-      </c>
+      <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr"/>
       <c r="Q13" s="3" t="inlineStr"/>
       <c r="R13" s="3" t="inlineStr">
@@ -2540,17 +2532,9 @@
           <t>8A ISLAMIAT</t>
         </is>
       </c>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t>10C SINDHI-X</t>
-        </is>
-      </c>
+      <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="inlineStr"/>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t>9A ISLAMIAT IX</t>
-        </is>
-      </c>
+      <c r="Z13" s="3" t="inlineStr"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>6C ISLAMIAT</t>
@@ -2606,8 +2590,16 @@
           <t>9B CHEMISTRY</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr"/>
-      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>10C MATHS</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr">
+        <is>
+          <t>9A CHEMISTRY</t>
+        </is>
+      </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
           <t>6B HISTORY</t>
@@ -2625,7 +2617,11 @@
           <t>10B GAMES</t>
         </is>
       </c>
-      <c r="AW13" s="3" t="inlineStr"/>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>6E GAMES</t>
+        </is>
+      </c>
       <c r="AX13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
@@ -2907,11 +2903,7 @@
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>8A COMPUTER</t>
-        </is>
-      </c>
+      <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr"/>
       <c r="U16" s="2" t="inlineStr">
         <is>
@@ -2934,7 +2926,11 @@
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr"/>
-      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>9A ISLAMIAT IX</t>
+        </is>
+      </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
           <t>6B ISLAMIAT</t>
@@ -2962,15 +2958,19 @@
         </is>
       </c>
       <c r="AG16" s="2" t="inlineStr"/>
-      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t>7D PH</t>
+        </is>
+      </c>
       <c r="AI16" s="2" t="inlineStr"/>
-      <c r="AJ16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>10E PHYSICS</t>
+        </is>
+      </c>
       <c r="AK16" s="2" t="inlineStr"/>
-      <c r="AL16" s="2" t="inlineStr">
-        <is>
-          <t>9A BIOLOGY</t>
-        </is>
-      </c>
+      <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr">
         <is>
           <t>10C PHYSICS</t>
@@ -2989,14 +2989,10 @@
       </c>
       <c r="AQ16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9F GENERAL SCIENCE </t>
-        </is>
-      </c>
-      <c r="AR16" s="2" t="inlineStr">
-        <is>
-          <t>7D S.ST</t>
-        </is>
-      </c>
+          <t>9F GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AR16" s="2" t="inlineStr"/>
       <c r="AS16" s="2" t="inlineStr">
         <is>
           <t>7E SINDHI</t>
@@ -3004,13 +3000,13 @@
       </c>
       <c r="AT16" s="2" t="inlineStr"/>
       <c r="AU16" s="2" t="inlineStr"/>
-      <c r="AV16" s="2" t="inlineStr">
-        <is>
-          <t>10E GAMES</t>
-        </is>
-      </c>
+      <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" s="2" t="inlineStr"/>
-      <c r="AX16" s="2" t="inlineStr"/>
+      <c r="AX16" s="2" t="inlineStr">
+        <is>
+          <t>8A AI</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr"/>
@@ -3123,25 +3119,25 @@
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr">
-        <is>
-          <t>9B LIBRARY</t>
-        </is>
-      </c>
+      <c r="AI17" s="3" t="inlineStr"/>
       <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>7C S.ST</t>
+        </is>
+      </c>
       <c r="AL17" s="3" t="inlineStr"/>
       <c r="AM17" s="3" t="inlineStr">
         <is>
           <t>10A PHYSICS</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr">
-        <is>
-          <t>9E CHEMISTRY</t>
-        </is>
-      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>9B BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr"/>
       <c r="AP17" s="3" t="inlineStr">
         <is>
           <t>10C MATHS</t>
@@ -3157,14 +3153,14 @@
           <t>8A HISTORY</t>
         </is>
       </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>7C SINDHI</t>
-        </is>
-      </c>
+      <c r="AS17" s="3" t="inlineStr"/>
       <c r="AT17" s="3" t="inlineStr"/>
       <c r="AU17" s="3" t="inlineStr"/>
-      <c r="AV17" s="3" t="inlineStr"/>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>9E GAMES</t>
+        </is>
+      </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
           <t>6B GAMES</t>
@@ -3694,11 +3690,7 @@
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>6B GENERAL SCIENCE</t>
-        </is>
-      </c>
+      <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
       <c r="M21" s="3" t="inlineStr">
@@ -3738,7 +3730,11 @@
           <t>10F ENGLISH</t>
         </is>
       </c>
-      <c r="V21" s="3" t="inlineStr"/>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>9F ENGLISH</t>
+        </is>
+      </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
           <t>8D ARABIC</t>
@@ -3780,11 +3776,7 @@
           <t>10B LIBRARY</t>
         </is>
       </c>
-      <c r="AJ21" s="3" t="inlineStr">
-        <is>
-          <t>10E PHYSICS</t>
-        </is>
-      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
       <c r="AK21" s="3" t="inlineStr">
         <is>
           <t>7C S.ST</t>
@@ -3795,11 +3787,7 @@
           <t>10A BIOLOGY</t>
         </is>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
-        <is>
-          <t>10C PHYSICS</t>
-        </is>
-      </c>
+      <c r="AM21" s="3" t="inlineStr"/>
       <c r="AN21" s="3" t="inlineStr">
         <is>
           <t>9B BIOLOGY</t>
@@ -3817,10 +3805,14 @@
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9F GENERAL SCIENCE </t>
-        </is>
-      </c>
-      <c r="AR21" s="3" t="inlineStr"/>
+          <t>10E CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>6B GEOGRAPHY</t>
+        </is>
+      </c>
       <c r="AS21" s="3" t="inlineStr"/>
       <c r="AT21" s="3" t="inlineStr"/>
       <c r="AU21" s="3" t="inlineStr"/>
@@ -3855,7 +3847,11 @@
       </c>
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8D GENERAL SCIENCE</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>7A URDU</t>
@@ -3877,11 +3873,7 @@
           <t>6E GENERAL SCIENCE</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>8D URDU</t>
-        </is>
-      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>6B ENGLISH</t>
@@ -3903,11 +3895,7 @@
           <t>9F COMPUTER IX-X</t>
         </is>
       </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>10E COMPUTER IX-X</t>
-        </is>
-      </c>
+      <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr">
         <is>
           <t>9E COMPUTER IX-X</t>
@@ -3963,7 +3951,11 @@
         </is>
       </c>
       <c r="AH22" s="2" t="inlineStr"/>
-      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr">
+        <is>
+          <t>10E LIBRARY</t>
+        </is>
+      </c>
       <c r="AJ22" s="2" t="inlineStr"/>
       <c r="AK22" s="2" t="inlineStr"/>
       <c r="AL22" s="2" t="inlineStr"/>
@@ -4074,7 +4066,7 @@
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>6B COMPUTER</t>
+          <t>9E COMPUTER IX-X</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr"/>
@@ -4095,11 +4087,7 @@
           <t>9A ISLAMIAT IX</t>
         </is>
       </c>
-      <c r="AA23" s="3" t="inlineStr">
-        <is>
-          <t>7C ARABIC</t>
-        </is>
-      </c>
+      <c r="AA23" s="3" t="inlineStr"/>
       <c r="AB23" s="3" t="inlineStr">
         <is>
           <t>10D SINDHI-X</t>
@@ -4153,16 +4141,20 @@
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr"/>
-      <c r="AS23" s="3" t="inlineStr"/>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>7C SINDHI</t>
+        </is>
+      </c>
       <c r="AT23" s="3" t="inlineStr"/>
       <c r="AU23" s="3" t="inlineStr"/>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>9E GAMES</t>
-        </is>
-      </c>
+      <c r="AV23" s="3" t="inlineStr"/>
       <c r="AW23" s="3" t="inlineStr"/>
-      <c r="AX23" s="3" t="inlineStr"/>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>6B AI</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr"/>
@@ -4232,25 +4224,29 @@
           <t>11:20-12:00</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>10C ENGLISH</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
           <t>9B MATHS</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>8D GENERAL SCIENCE</t>
-        </is>
-      </c>
+      <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
           <t>6D URDU</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>6B GENERAL SCIENCE</t>
+        </is>
+      </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
           <t>9C URDU</t>
@@ -4286,11 +4282,7 @@
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>9F ENGLISH</t>
-        </is>
-      </c>
+      <c r="V25" s="3" t="inlineStr"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
           <t>7D ARABIC</t>
@@ -4336,7 +4328,11 @@
           <t>9A LIBRARY</t>
         </is>
       </c>
-      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AJ25" s="3" t="inlineStr">
+        <is>
+          <t>10E PHYSICS</t>
+        </is>
+      </c>
       <c r="AK25" s="3" t="inlineStr"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
@@ -4357,7 +4353,7 @@
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>10E CHEMISTRY</t>
+          <t>9F GENERAL SCIENCE</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
@@ -4374,15 +4370,11 @@
       <c r="AU25" s="3" t="inlineStr"/>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>10C GAMES</t>
+          <t>8D GAMES</t>
         </is>
       </c>
       <c r="AW25" s="3" t="inlineStr"/>
-      <c r="AX25" s="3" t="inlineStr">
-        <is>
-          <t>6B AI</t>
-        </is>
-      </c>
+      <c r="AX25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr"/>
@@ -4464,7 +4456,11 @@
           <t>8D ISLAMIAT</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>10C SINDHI-X</t>
+        </is>
+      </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>6E ARABIC</t>
@@ -4526,11 +4522,7 @@
           <t>9E CHEMISTRY</t>
         </is>
       </c>
-      <c r="AP26" s="2" t="inlineStr">
-        <is>
-          <t>10C MATHS</t>
-        </is>
-      </c>
+      <c r="AP26" s="2" t="inlineStr"/>
       <c r="AQ26" s="2" t="inlineStr"/>
       <c r="AR26" s="2" t="inlineStr">
         <is>
@@ -4724,11 +4716,7 @@
           <t>1:20-2:00</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>10C ENGLISH</t>
-        </is>
-      </c>
+      <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>7B MATHS</t>
@@ -4761,7 +4749,11 @@
           <t xml:space="preserve">10F GENERAL SCIENCE </t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>8D URDU</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -4817,17 +4809,17 @@
           <t>8A GEOGRAPHY</t>
         </is>
       </c>
-      <c r="AG28" s="2" t="inlineStr">
-        <is>
-          <t>8D S.ST</t>
-        </is>
-      </c>
+      <c r="AG28" s="2" t="inlineStr"/>
       <c r="AH28" s="2" t="inlineStr">
         <is>
           <t>9E ISLAMIAT IX</t>
         </is>
       </c>
-      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr">
+        <is>
+          <t>10C LIBRARY</t>
+        </is>
+      </c>
       <c r="AJ28" s="2" t="inlineStr"/>
       <c r="AK28" s="2" t="inlineStr"/>
       <c r="AL28" s="2" t="inlineStr">
@@ -4939,7 +4931,11 @@
           <t>7E ENGLISH</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>7D MATHS</t>
+        </is>
+      </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
           <t>6B MATHS</t>
@@ -4998,11 +4994,7 @@
           <t>9F ECONOMICS</t>
         </is>
       </c>
-      <c r="AH29" s="3" t="inlineStr">
-        <is>
-          <t>7D PH</t>
-        </is>
-      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
       <c r="AI29" s="3" t="inlineStr"/>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
@@ -5106,11 +5098,7 @@
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>8D COMPUTER</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
       <c r="S30" s="2" t="inlineStr">
         <is>
           <t>10E COMPUTER IX-X</t>
@@ -5145,18 +5133,18 @@
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr"/>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>10A MATHS</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
           <t>7C MATHS</t>
         </is>
       </c>
       <c r="AE30" s="2" t="inlineStr"/>
-      <c r="AF30" s="2" t="inlineStr">
-        <is>
-          <t>10A PAKISTAN STUDIES</t>
-        </is>
-      </c>
+      <c r="AF30" s="2" t="inlineStr"/>
       <c r="AG30" s="2" t="inlineStr">
         <is>
           <t>8C S.ST</t>
@@ -5174,7 +5162,11 @@
         </is>
       </c>
       <c r="AK30" s="2" t="inlineStr"/>
-      <c r="AL30" s="2" t="inlineStr"/>
+      <c r="AL30" s="2" t="inlineStr">
+        <is>
+          <t>9A BIOLOGY</t>
+        </is>
+      </c>
       <c r="AM30" s="2" t="inlineStr">
         <is>
           <t>10C PHYSICS</t>
@@ -5197,14 +5189,14 @@
           <t>8A HISTORY</t>
         </is>
       </c>
-      <c r="AS30" s="2" t="inlineStr"/>
+      <c r="AS30" s="2" t="inlineStr">
+        <is>
+          <t>8D SINDHI</t>
+        </is>
+      </c>
       <c r="AT30" s="2" t="inlineStr"/>
       <c r="AU30" s="2" t="inlineStr"/>
-      <c r="AV30" s="2" t="inlineStr">
-        <is>
-          <t>9A GAMES</t>
-        </is>
-      </c>
+      <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" s="2" t="inlineStr"/>
       <c r="AX30" s="2" t="inlineStr"/>
     </row>
@@ -5308,18 +5300,18 @@
           <t>10F MATHS</t>
         </is>
       </c>
-      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>10A PAKISTAN STUDIES</t>
+        </is>
+      </c>
       <c r="AG31" s="3" t="inlineStr"/>
       <c r="AH31" s="3" t="inlineStr">
         <is>
           <t>9E ISLAMIAT IX</t>
         </is>
       </c>
-      <c r="AI31" s="3" t="inlineStr">
-        <is>
-          <t>10C LIBRARY</t>
-        </is>
-      </c>
+      <c r="AI31" s="3" t="inlineStr"/>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
           <t>10E PHYSICS</t>
@@ -5333,7 +5325,7 @@
       <c r="AL31" s="3" t="inlineStr"/>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>10A PHYSICS</t>
+          <t>10C PHYSICS</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
@@ -5352,11 +5344,7 @@
           <t>9A CHEMISTRY</t>
         </is>
       </c>
-      <c r="AR31" s="3" t="inlineStr">
-        <is>
-          <t>6A HISTORY</t>
-        </is>
-      </c>
+      <c r="AR31" s="3" t="inlineStr"/>
       <c r="AS31" s="3" t="inlineStr">
         <is>
           <t>6E SINDHI</t>
@@ -5370,7 +5358,11 @@
         </is>
       </c>
       <c r="AW31" s="3" t="inlineStr"/>
-      <c r="AX31" s="3" t="inlineStr"/>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>6A AI</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr"/>
@@ -5412,7 +5404,11 @@
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>6E GENERAL SCIENCE</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
           <t>9F URDU</t>
@@ -5457,11 +5453,7 @@
           <t>10A SINDHI-X</t>
         </is>
       </c>
-      <c r="Y32" s="2" t="inlineStr">
-        <is>
-          <t>6E ISLAMIAT</t>
-        </is>
-      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
       <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>6D ARABIC</t>
@@ -5626,24 +5618,24 @@
           <t>6C ENGLISH</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>6B GENERAL SCIENCE</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
           <t>9B URDU</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>6E GENERAL SCIENCE</t>
-        </is>
-      </c>
+      <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>7D MATHS</t>
-        </is>
-      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>7B S.ST</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
           <t>9C MATHS</t>
@@ -5655,7 +5647,11 @@
           <t>8C COMPUTER</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>6E COMPUTER</t>
+        </is>
+      </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
           <t>10F COMPUTER IX-X</t>
@@ -5681,11 +5677,7 @@
           <t>10E SINDHI-X</t>
         </is>
       </c>
-      <c r="Y34" s="2" t="inlineStr">
-        <is>
-          <t>7B ISLAMIAT</t>
-        </is>
-      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
       <c r="Z34" s="2" t="inlineStr">
         <is>
           <t>9F ISLAMIAT IX</t>
@@ -5705,7 +5697,11 @@
       </c>
       <c r="AE34" s="2" t="inlineStr"/>
       <c r="AF34" s="2" t="inlineStr"/>
-      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>8D S.ST</t>
+        </is>
+      </c>
       <c r="AH34" s="2" t="inlineStr">
         <is>
           <t>8B ISLAMIAT</t>
@@ -5734,14 +5730,10 @@
       <c r="AQ34" s="2" t="inlineStr"/>
       <c r="AR34" s="2" t="inlineStr">
         <is>
-          <t>6B GEOGRAPHY</t>
-        </is>
-      </c>
-      <c r="AS34" s="2" t="inlineStr">
-        <is>
-          <t>8D SINDHI</t>
-        </is>
-      </c>
+          <t>7D S.ST</t>
+        </is>
+      </c>
+      <c r="AS34" s="2" t="inlineStr"/>
       <c r="AT34" s="2" t="inlineStr"/>
       <c r="AU34" s="2" t="inlineStr"/>
       <c r="AV34" s="2" t="inlineStr">
@@ -5768,7 +5760,11 @@
           <t>12:10-12:45</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>7D ENGLISH</t>
+        </is>
+      </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
           <t>7B MATHS</t>
@@ -5782,11 +5778,7 @@
       <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="3" t="inlineStr"/>
       <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>6B GENERAL SCIENCE</t>
-        </is>
-      </c>
+      <c r="J35" s="3" t="inlineStr"/>
       <c r="K35" s="3" t="inlineStr"/>
       <c r="L35" s="3" t="inlineStr">
         <is>
@@ -5819,8 +5811,16 @@
           <t>6A COMPUTER</t>
         </is>
       </c>
-      <c r="S35" s="3" t="inlineStr"/>
-      <c r="T35" s="3" t="inlineStr"/>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>8A COMPUTER</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t>6B COMPUTER</t>
+        </is>
+      </c>
       <c r="U35" s="3" t="inlineStr"/>
       <c r="V35" s="3" t="inlineStr"/>
       <c r="W35" s="3" t="inlineStr">
@@ -5863,11 +5863,7 @@
           <t>9B ISLAMIAT IX</t>
         </is>
       </c>
-      <c r="AI35" s="3" t="inlineStr">
-        <is>
-          <t>10A LIBRARY</t>
-        </is>
-      </c>
+      <c r="AI35" s="3" t="inlineStr"/>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
           <t>9E PHYSICS</t>
@@ -5884,7 +5880,11 @@
           <t>9C PHYSICS</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr"/>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>10A CHEMISTRY</t>
+        </is>
+      </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>9D CHEMISTRY</t>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9F GENERAL SCIENCE </t>
+          <t>9F GENERAL SCIENCE</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr"/>
@@ -5909,16 +5909,8 @@
       <c r="AT35" s="3" t="inlineStr"/>
       <c r="AU35" s="3" t="inlineStr"/>
       <c r="AV35" s="3" t="inlineStr"/>
-      <c r="AW35" s="3" t="inlineStr">
-        <is>
-          <t>7D GAMES</t>
-        </is>
-      </c>
-      <c r="AX35" s="3" t="inlineStr">
-        <is>
-          <t>8A AI</t>
-        </is>
-      </c>
+      <c r="AW35" s="3" t="inlineStr"/>
+      <c r="AX35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr"/>
@@ -6096,11 +6088,7 @@
           <t>1:15-2:00</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>7D ENGLISH</t>
-        </is>
-      </c>
+      <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr"/>
@@ -6151,11 +6139,7 @@
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t>8A COMPUTER</t>
-        </is>
-      </c>
+      <c r="S37" s="3" t="inlineStr"/>
       <c r="T37" s="3" t="inlineStr"/>
       <c r="U37" s="3" t="inlineStr">
         <is>
@@ -6167,11 +6151,15 @@
           <t>9F ENGLISH</t>
         </is>
       </c>
-      <c r="W37" s="3" t="inlineStr"/>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>8A ARABIC</t>
+        </is>
+      </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>6E ARABIC</t>
+          <t>6E ISLAMIAT</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
@@ -6211,12 +6199,12 @@
         </is>
       </c>
       <c r="AL37" s="3" t="inlineStr"/>
-      <c r="AM37" s="3" t="inlineStr"/>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>10A CHEMISTRY</t>
-        </is>
-      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>10A PHYSICS</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr"/>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>9B PHYSICS</t>
@@ -6245,7 +6233,11 @@
       <c r="AT37" s="3" t="inlineStr"/>
       <c r="AU37" s="3" t="inlineStr"/>
       <c r="AV37" s="3" t="inlineStr"/>
-      <c r="AW37" s="3" t="inlineStr"/>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>7D GAMES</t>
+        </is>
+      </c>
       <c r="AX37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
@@ -6286,7 +6278,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>7D GENERAL SCIENCE</t>
+        </is>
+      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
           <t>9C URDU</t>
@@ -6321,7 +6317,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6E COMPUTER</t>
+          <t>8A COMPUTER</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr"/>
@@ -6331,11 +6327,7 @@
           <t>9E ENGLISH</t>
         </is>
       </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>7D ISLAMIAT</t>
-        </is>
-      </c>
+      <c r="W38" s="2" t="inlineStr"/>
       <c r="X38" s="2" t="inlineStr">
         <is>
           <t>10E SINDHI-X</t>
@@ -6372,11 +6364,7 @@
           <t>10F MATHS</t>
         </is>
       </c>
-      <c r="AF38" s="2" t="inlineStr">
-        <is>
-          <t>8A GEOGRAPHY</t>
-        </is>
-      </c>
+      <c r="AF38" s="2" t="inlineStr"/>
       <c r="AG38" s="2" t="inlineStr">
         <is>
           <t>9F ECONOMICS</t>
@@ -6409,7 +6397,11 @@
           <t>6B GEOGRAPHY</t>
         </is>
       </c>
-      <c r="AS38" s="2" t="inlineStr"/>
+      <c r="AS38" s="2" t="inlineStr">
+        <is>
+          <t>6E SINDHI</t>
+        </is>
+      </c>
       <c r="AT38" s="2" t="inlineStr"/>
       <c r="AU38" s="2" t="inlineStr"/>
       <c r="AV38" s="2" t="inlineStr"/>
@@ -6483,7 +6475,11 @@
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr"/>
-      <c r="S39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>6E COMPUTER</t>
+        </is>
+      </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
           <t>6B COMPUTER</t>
@@ -6517,11 +6513,7 @@
           <t>10F SINDHI-X</t>
         </is>
       </c>
-      <c r="AC39" s="3" t="inlineStr">
-        <is>
-          <t>10A MATHS</t>
-        </is>
-      </c>
+      <c r="AC39" s="3" t="inlineStr"/>
       <c r="AD39" s="3" t="inlineStr">
         <is>
           <t>9D PHYSICS</t>
@@ -6543,7 +6535,11 @@
           <t>9C ISLAMIAT IX</t>
         </is>
       </c>
-      <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>10A LIBRARY</t>
+        </is>
+      </c>
       <c r="AJ39" s="3" t="inlineStr"/>
       <c r="AK39" s="3" t="inlineStr"/>
       <c r="AL39" s="3" t="inlineStr"/>
@@ -6569,11 +6565,7 @@
           <t>8A HISTORY</t>
         </is>
       </c>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>6E SINDHI</t>
-        </is>
-      </c>
+      <c r="AS39" s="3" t="inlineStr"/>
       <c r="AT39" s="3" t="inlineStr"/>
       <c r="AU39" s="3" t="inlineStr"/>
       <c r="AV39" s="3" t="inlineStr"/>
@@ -6646,7 +6638,11 @@
           <t>9D URDU</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>8D COMPUTER</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
@@ -6700,11 +6696,7 @@
       </c>
       <c r="AH40" s="2" t="inlineStr"/>
       <c r="AI40" s="2" t="inlineStr"/>
-      <c r="AJ40" s="2" t="inlineStr">
-        <is>
-          <t>10E PHYSICS</t>
-        </is>
-      </c>
+      <c r="AJ40" s="2" t="inlineStr"/>
       <c r="AK40" s="2" t="inlineStr">
         <is>
           <t>10A ENGLISH</t>
@@ -6733,14 +6725,14 @@
         </is>
       </c>
       <c r="AR40" s="2" t="inlineStr"/>
-      <c r="AS40" s="2" t="inlineStr">
-        <is>
-          <t>8D SINDHI</t>
-        </is>
-      </c>
+      <c r="AS40" s="2" t="inlineStr"/>
       <c r="AT40" s="2" t="inlineStr"/>
       <c r="AU40" s="2" t="inlineStr"/>
-      <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AV40" s="2" t="inlineStr">
+        <is>
+          <t>10E GAMES</t>
+        </is>
+      </c>
       <c r="AW40" s="2" t="inlineStr"/>
       <c r="AX40" s="2" t="inlineStr"/>
     </row>
@@ -6778,11 +6770,7 @@
           <t>6D ENGLISH</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>7D GENERAL SCIENCE</t>
-        </is>
-      </c>
+      <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
           <t>8A URDU</t>
@@ -6803,7 +6791,11 @@
           <t>6E ENGLISH</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>7D MATHS</t>
+        </is>
+      </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
           <t>6B MATHS</t>
@@ -6889,7 +6881,7 @@
       <c r="AP41" s="3" t="inlineStr"/>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9F GENERAL SCIENCE </t>
+          <t>9F GENERAL SCIENCE</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr"/>
@@ -7112,7 +7104,11 @@
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
-      <c r="AR43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>6A HISTORY</t>
+        </is>
+      </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
           <t>7D SINDHI</t>
@@ -7122,11 +7118,7 @@
       <c r="AU43" s="3" t="inlineStr"/>
       <c r="AV43" s="3" t="inlineStr"/>
       <c r="AW43" s="3" t="inlineStr"/>
-      <c r="AX43" s="3" t="inlineStr">
-        <is>
-          <t>6A AI</t>
-        </is>
-      </c>
+      <c r="AX43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr"/>
@@ -7267,7 +7259,11 @@
           <t>10B BIOLOGY</t>
         </is>
       </c>
-      <c r="AM44" s="2" t="inlineStr"/>
+      <c r="AM44" s="2" t="inlineStr">
+        <is>
+          <t>9A PHYSICS</t>
+        </is>
+      </c>
       <c r="AN44" s="2" t="inlineStr">
         <is>
           <t>9B BIOLOGY</t>
@@ -7279,11 +7275,7 @@
         </is>
       </c>
       <c r="AP44" s="2" t="inlineStr"/>
-      <c r="AQ44" s="2" t="inlineStr">
-        <is>
-          <t>9A CHEMISTRY</t>
-        </is>
-      </c>
+      <c r="AQ44" s="2" t="inlineStr"/>
       <c r="AR44" s="2" t="inlineStr"/>
       <c r="AS44" s="2" t="inlineStr"/>
       <c r="AT44" s="2" t="inlineStr"/>

--- a/school_timetable.xlsx
+++ b/school_timetable.xlsx
@@ -467,7 +467,7 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
@@ -1846,7 +1846,7 @@
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10F GENERAL SCIENCE </t>
+          <t>10F GENERAL SCIENCE</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr"/>
@@ -2059,11 +2059,7 @@
           <t>6D ISLAMIAT</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>6B ARABIC</t>
-        </is>
-      </c>
+      <c r="AA10" s="2" t="inlineStr"/>
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
@@ -2125,7 +2121,11 @@
       <c r="AT10" s="2" t="inlineStr"/>
       <c r="AU10" s="2" t="inlineStr"/>
       <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr">
+        <is>
+          <t>6B GAMES</t>
+        </is>
+      </c>
       <c r="AX10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
@@ -2506,11 +2506,7 @@
       <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr"/>
       <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t>9F COMPUTER IX-X</t>
-        </is>
-      </c>
+      <c r="R13" s="3" t="inlineStr"/>
       <c r="S13" s="3" t="inlineStr"/>
       <c r="T13" s="3" t="inlineStr">
         <is>
@@ -2534,7 +2530,11 @@
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="inlineStr"/>
-      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>9F ISLAMIAT IX</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>6C ISLAMIAT</t>
@@ -2577,12 +2577,12 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr">
         <is>
-          <t>9C PHYSICS</t>
+          <t>10A PHYSICS</t>
         </is>
       </c>
       <c r="AN13" s="3" t="inlineStr">
         <is>
-          <t>10A CHEMISTRY</t>
+          <t>9C CHEMISTRY</t>
         </is>
       </c>
       <c r="AO13" s="3" t="inlineStr">
@@ -3020,11 +3020,7 @@
           <t>12:00-12:40</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>9C ENGLISH</t>
-        </is>
-      </c>
+      <c r="D17" s="3" t="inlineStr"/>
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>9F MATHS</t>
@@ -3088,18 +3084,18 @@
       <c r="U17" s="3" t="inlineStr"/>
       <c r="V17" s="3" t="inlineStr"/>
       <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t>10E SINDHI-X</t>
-        </is>
-      </c>
+      <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>7E ISLAMIAT</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr"/>
-      <c r="AA17" s="3" t="inlineStr"/>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>6B ARABIC</t>
+        </is>
+      </c>
       <c r="AB17" s="3" t="inlineStr"/>
       <c r="AC17" s="3" t="inlineStr">
         <is>
@@ -3112,7 +3108,11 @@
           <t>9D MATHS</t>
         </is>
       </c>
-      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>10A PAKISTAN STUDIES</t>
+        </is>
+      </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
           <t>8C S.ST</t>
@@ -3120,7 +3120,11 @@
       </c>
       <c r="AH17" s="3" t="inlineStr"/>
       <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr">
+        <is>
+          <t>10E PHYSICS</t>
+        </is>
+      </c>
       <c r="AK17" s="3" t="inlineStr">
         <is>
           <t>7C S.ST</t>
@@ -3129,7 +3133,7 @@
       <c r="AL17" s="3" t="inlineStr"/>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>10A PHYSICS</t>
+          <t>9C PHYSICS</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -3161,11 +3165,7 @@
           <t>9E GAMES</t>
         </is>
       </c>
-      <c r="AW17" s="3" t="inlineStr">
-        <is>
-          <t>6B GAMES</t>
-        </is>
-      </c>
+      <c r="AW17" s="3" t="inlineStr"/>
       <c r="AX17" s="3" t="inlineStr">
         <is>
           <t>6A AI</t>
@@ -3260,7 +3260,11 @@
           <t>8C ARABIC</t>
         </is>
       </c>
-      <c r="X18" s="2" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>10E SINDHI-X</t>
+        </is>
+      </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>7B ARABIC</t>
@@ -3268,7 +3272,11 @@
       </c>
       <c r="Z18" s="2" t="inlineStr"/>
       <c r="AA18" s="2" t="inlineStr"/>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>10B SINDHI-X</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
@@ -3288,11 +3296,7 @@
         </is>
       </c>
       <c r="AI18" s="2" t="inlineStr"/>
-      <c r="AJ18" s="2" t="inlineStr">
-        <is>
-          <t>10E PHYSICS</t>
-        </is>
-      </c>
+      <c r="AJ18" s="2" t="inlineStr"/>
       <c r="AK18" s="2" t="inlineStr">
         <is>
           <t>9D ENGLISH</t>
@@ -3310,11 +3314,7 @@
           <t>10D CHEMISTRY</t>
         </is>
       </c>
-      <c r="AP18" s="2" t="inlineStr">
-        <is>
-          <t>10B MATHS</t>
-        </is>
-      </c>
+      <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr">
         <is>
@@ -3348,7 +3348,11 @@
           <t>1:20-2:00</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>9C ENGLISH</t>
+        </is>
+      </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3370,7 +3374,7 @@
       <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10F GENERAL SCIENCE </t>
+          <t>10F GENERAL SCIENCE</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -3428,11 +3432,7 @@
           <t>7A ISLAMIAT</t>
         </is>
       </c>
-      <c r="AB19" s="3" t="inlineStr">
-        <is>
-          <t>10B SINDHI-X</t>
-        </is>
-      </c>
+      <c r="AB19" s="3" t="inlineStr"/>
       <c r="AC19" s="3" t="inlineStr">
         <is>
           <t>8A MATHS</t>
@@ -3444,11 +3444,7 @@
         </is>
       </c>
       <c r="AE19" s="3" t="inlineStr"/>
-      <c r="AF19" s="3" t="inlineStr">
-        <is>
-          <t>10A PAKISTAN STUDIES</t>
-        </is>
-      </c>
+      <c r="AF19" s="3" t="inlineStr"/>
       <c r="AG19" s="3" t="inlineStr">
         <is>
           <t>8D S.ST</t>
@@ -3478,7 +3474,7 @@
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>9C CHEMISTRY</t>
+          <t>10A CHEMISTRY</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
@@ -3486,7 +3482,11 @@
           <t>9D CHEMISTRY</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>10B MATHS</t>
+        </is>
+      </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
           <t>10C CHEMISTRY</t>
@@ -3845,7 +3845,11 @@
           <t>9C ENGLISH</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9F MATHS</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -3890,11 +3894,7 @@
           <t>7E URDU</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>9F COMPUTER IX-X</t>
-        </is>
-      </c>
+      <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr">
         <is>
@@ -4389,11 +4389,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>9F MATHS</t>
-        </is>
-      </c>
+      <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>10E PAKISTAN STUDIES</t>
@@ -4434,7 +4430,11 @@
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>9F COMPUTER IX-X</t>
+        </is>
+      </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
           <t>6C COMPUTER</t>
@@ -4746,7 +4746,7 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10F GENERAL SCIENCE </t>
+          <t>10F GENERAL SCIENCE</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -5678,11 +5678,7 @@
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr"/>
-      <c r="Z34" s="2" t="inlineStr">
-        <is>
-          <t>9F ISLAMIAT IX</t>
-        </is>
-      </c>
+      <c r="Z34" s="2" t="inlineStr"/>
       <c r="AA34" s="2" t="inlineStr"/>
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
@@ -5727,7 +5723,11 @@
           <t>9E MATHS</t>
         </is>
       </c>
-      <c r="AQ34" s="2" t="inlineStr"/>
+      <c r="AQ34" s="2" t="inlineStr">
+        <is>
+          <t>9F GENERAL SCIENCE</t>
+        </is>
+      </c>
       <c r="AR34" s="2" t="inlineStr">
         <is>
           <t>7D S.ST</t>
@@ -5782,7 +5782,7 @@
       <c r="K35" s="3" t="inlineStr"/>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10F GENERAL SCIENCE </t>
+          <t>10F GENERAL SCIENCE</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -5822,7 +5822,11 @@
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr"/>
-      <c r="V35" s="3" t="inlineStr"/>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>9F ENGLISH</t>
+        </is>
+      </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
           <t>8D ARABIC</t>
@@ -5895,11 +5899,7 @@
           <t>10C MATHS</t>
         </is>
       </c>
-      <c r="AQ35" s="3" t="inlineStr">
-        <is>
-          <t>9F GENERAL SCIENCE</t>
-        </is>
-      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr"/>
       <c r="AS35" s="3" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10F GENERAL SCIENCE </t>
+          <t>10F GENERAL SCIENCE</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -6138,7 +6138,11 @@
           <t>9A URDU</t>
         </is>
       </c>
-      <c r="R37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>9F COMPUTER IX-X</t>
+        </is>
+      </c>
       <c r="S37" s="3" t="inlineStr"/>
       <c r="T37" s="3" t="inlineStr"/>
       <c r="U37" s="3" t="inlineStr">
@@ -6146,11 +6150,7 @@
           <t>10E ENGLISH</t>
         </is>
       </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t>9F ENGLISH</t>
-        </is>
-      </c>
+      <c r="V37" s="3" t="inlineStr"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
           <t>8A ARABIC</t>
@@ -6373,7 +6373,11 @@
       <c r="AH38" s="2" t="inlineStr"/>
       <c r="AI38" s="2" t="inlineStr"/>
       <c r="AJ38" s="2" t="inlineStr"/>
-      <c r="AK38" s="2" t="inlineStr"/>
+      <c r="AK38" s="2" t="inlineStr">
+        <is>
+          <t>9B ENGLISH</t>
+        </is>
+      </c>
       <c r="AL38" s="2" t="inlineStr">
         <is>
           <t>10D BIOLOGY</t>
@@ -6381,11 +6385,7 @@
       </c>
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr"/>
-      <c r="AO38" s="2" t="inlineStr">
-        <is>
-          <t>9B PHYSICS</t>
-        </is>
-      </c>
+      <c r="AO38" s="2" t="inlineStr"/>
       <c r="AP38" s="2" t="inlineStr">
         <is>
           <t>10B MATHS</t>
@@ -6589,11 +6589,7 @@
           <t>7D ENGLISH</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>9B MATHS</t>
-        </is>
-      </c>
+      <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
           <t>10D PAKISTAN STUDIES</t>
@@ -6713,7 +6709,11 @@
           <t>9C CHEMISTRY</t>
         </is>
       </c>
-      <c r="AO40" s="2" t="inlineStr"/>
+      <c r="AO40" s="2" t="inlineStr">
+        <is>
+          <t>9B PHYSICS</t>
+        </is>
+      </c>
       <c r="AP40" s="2" t="inlineStr">
         <is>
           <t>10C MATHS</t>
@@ -6753,7 +6753,11 @@
           <t>6A ENGLISH</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>9B MATHS</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -6857,11 +6861,7 @@
       </c>
       <c r="AI41" s="3" t="inlineStr"/>
       <c r="AJ41" s="3" t="inlineStr"/>
-      <c r="AK41" s="3" t="inlineStr">
-        <is>
-          <t>9B ENGLISH</t>
-        </is>
-      </c>
+      <c r="AK41" s="3" t="inlineStr"/>
       <c r="AL41" s="3" t="inlineStr"/>
       <c r="AM41" s="3" t="inlineStr">
         <is>

--- a/school_timetable.xlsx
+++ b/school_timetable.xlsx
@@ -1138,7 +1138,11 @@
       </c>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6E ENGLISH</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -1173,11 +1177,7 @@
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>6E ARABIC</t>
-        </is>
-      </c>
+      <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="inlineStr">
         <is>
@@ -1302,11 +1302,7 @@
           <t>9F URDU</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>6B ENGLISH</t>
-        </is>
-      </c>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
           <t>8D MATHS</t>
@@ -1317,7 +1313,11 @@
           <t>6A MATHS</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>6B URDU</t>
+        </is>
+      </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
           <t>7E COMPUTER</t>
@@ -1852,7 +1852,7 @@
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>6E ENGLISH</t>
+          <t>6B ENGLISH</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr"/>
@@ -1861,16 +1861,8 @@
           <t>9C MATHS</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>6B URDU</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>7A COMPUTER</t>
-        </is>
-      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
           <t>10E COMPUTER IX-X</t>
@@ -1893,7 +1885,11 @@
           <t>10A SINDHI-X</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>6E ARABIC</t>
+        </is>
+      </c>
       <c r="Z9" s="3" t="inlineStr"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1931,7 +1927,11 @@
           <t>7E PH</t>
         </is>
       </c>
-      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>9A LIBRARY</t>
+        </is>
+      </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
           <t>9E PHYSICS</t>
@@ -1952,13 +1952,17 @@
           <t>10C CHEMISTRY</t>
         </is>
       </c>
-      <c r="AR9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>7A HISTORY</t>
+        </is>
+      </c>
       <c r="AS9" s="3" t="inlineStr"/>
       <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" s="3" t="inlineStr"/>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>9A GAMES</t>
+          <t>9B GAMES</t>
         </is>
       </c>
       <c r="AW9" s="3" t="inlineStr"/>
@@ -2022,7 +2026,11 @@
           <t>7E URDU</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>7A COMPUTER</t>
+        </is>
+      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
           <t>10E COMPUTER IX-X</t>
@@ -2112,21 +2120,17 @@
         </is>
       </c>
       <c r="AQ10" s="2" t="inlineStr"/>
-      <c r="AR10" s="2" t="inlineStr">
-        <is>
-          <t>7A HISTORY</t>
-        </is>
-      </c>
+      <c r="AR10" s="2" t="inlineStr"/>
       <c r="AS10" s="2" t="inlineStr"/>
       <c r="AT10" s="2" t="inlineStr"/>
       <c r="AU10" s="2" t="inlineStr"/>
       <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr">
-        <is>
-          <t>6B GAMES</t>
-        </is>
-      </c>
-      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr"/>
+      <c r="AX10" s="2" t="inlineStr">
+        <is>
+          <t>6B AI</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2781,12 +2785,12 @@
           <t>9C GAMES</t>
         </is>
       </c>
-      <c r="AW14" s="2" t="inlineStr"/>
-      <c r="AX14" s="2" t="inlineStr">
-        <is>
-          <t>6B AI</t>
-        </is>
-      </c>
+      <c r="AW14" s="2" t="inlineStr">
+        <is>
+          <t>6B GAMES</t>
+        </is>
+      </c>
+      <c r="AX14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr"/>
@@ -3714,7 +3718,11 @@
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>7E COMPUTER</t>
+        </is>
+      </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
           <t>8A COMPUTER</t>
@@ -3821,11 +3829,7 @@
           <t>8B GAMES</t>
         </is>
       </c>
-      <c r="AW21" s="3" t="inlineStr">
-        <is>
-          <t>7E GAMES</t>
-        </is>
-      </c>
+      <c r="AW21" s="3" t="inlineStr"/>
       <c r="AX21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
@@ -4266,11 +4270,7 @@
       <c r="O25" s="3" t="inlineStr"/>
       <c r="P25" s="3" t="inlineStr"/>
       <c r="Q25" s="3" t="inlineStr"/>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>7E COMPUTER</t>
-        </is>
-      </c>
+      <c r="R25" s="3" t="inlineStr"/>
       <c r="S25" s="3" t="inlineStr">
         <is>
           <t>6E COMPUTER</t>
@@ -4281,7 +4281,11 @@
           <t>7C COMPUTER</t>
         </is>
       </c>
-      <c r="U25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9A ENGLISH</t>
+        </is>
+      </c>
       <c r="V25" s="3" t="inlineStr"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
@@ -4323,11 +4327,7 @@
       </c>
       <c r="AG25" s="3" t="inlineStr"/>
       <c r="AH25" s="3" t="inlineStr"/>
-      <c r="AI25" s="3" t="inlineStr">
-        <is>
-          <t>9A LIBRARY</t>
-        </is>
-      </c>
+      <c r="AI25" s="3" t="inlineStr"/>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
           <t>10E PHYSICS</t>
@@ -4373,7 +4373,11 @@
           <t>8D GAMES</t>
         </is>
       </c>
-      <c r="AW25" s="3" t="inlineStr"/>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>7E GAMES</t>
+        </is>
+      </c>
       <c r="AX25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
@@ -4441,11 +4445,7 @@
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr"/>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>9A ENGLISH</t>
-        </is>
-      </c>
+      <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
           <t>8B ENGLISH</t>
@@ -4536,7 +4536,11 @@
       </c>
       <c r="AT26" s="2" t="inlineStr"/>
       <c r="AU26" s="2" t="inlineStr"/>
-      <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AV26" s="2" t="inlineStr">
+        <is>
+          <t>9A GAMES</t>
+        </is>
+      </c>
       <c r="AW26" s="2" t="inlineStr"/>
       <c r="AX26" s="2" t="inlineStr"/>
     </row>
@@ -5376,11 +5380,7 @@
           <t>10:40-11:15</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>6A ENGLISH</t>
-        </is>
-      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -5422,7 +5422,11 @@
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>6A COMPUTER</t>
+        </is>
+      </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
           <t>7D COMPUTER</t>
@@ -5762,7 +5766,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>7D ENGLISH</t>
+          <t>6A ENGLISH</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -5806,11 +5810,7 @@
           <t>7E URDU</t>
         </is>
       </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>6A COMPUTER</t>
-        </is>
-      </c>
+      <c r="R35" s="3" t="inlineStr"/>
       <c r="S35" s="3" t="inlineStr">
         <is>
           <t>8A COMPUTER</t>
@@ -5909,7 +5909,11 @@
       <c r="AT35" s="3" t="inlineStr"/>
       <c r="AU35" s="3" t="inlineStr"/>
       <c r="AV35" s="3" t="inlineStr"/>
-      <c r="AW35" s="3" t="inlineStr"/>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>7D GAMES</t>
+        </is>
+      </c>
       <c r="AX35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
@@ -5983,11 +5987,7 @@
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr"/>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>7D ISLAMIAT</t>
-        </is>
-      </c>
+      <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr">
         <is>
           <t>10C SINDHI-X</t>
@@ -6069,7 +6069,11 @@
           <t>6B HISTORY</t>
         </is>
       </c>
-      <c r="AS36" s="2" t="inlineStr"/>
+      <c r="AS36" s="2" t="inlineStr">
+        <is>
+          <t>7D SINDHI</t>
+        </is>
+      </c>
       <c r="AT36" s="2" t="inlineStr"/>
       <c r="AU36" s="2" t="inlineStr"/>
       <c r="AV36" s="2" t="inlineStr"/>
@@ -6088,7 +6092,11 @@
           <t>1:15-2:00</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>7D ENGLISH</t>
+        </is>
+      </c>
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr"/>
@@ -6233,11 +6241,7 @@
       <c r="AT37" s="3" t="inlineStr"/>
       <c r="AU37" s="3" t="inlineStr"/>
       <c r="AV37" s="3" t="inlineStr"/>
-      <c r="AW37" s="3" t="inlineStr">
-        <is>
-          <t>7D GAMES</t>
-        </is>
-      </c>
+      <c r="AW37" s="3" t="inlineStr"/>
       <c r="AX37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
@@ -6294,7 +6298,11 @@
           <t>8C URDU</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>7E ENGLISH</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
           <t>8D MATHS</t>
@@ -6333,11 +6341,7 @@
           <t>10E SINDHI-X</t>
         </is>
       </c>
-      <c r="Y38" s="2" t="inlineStr">
-        <is>
-          <t>7E ARABIC</t>
-        </is>
-      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
       <c r="Z38" s="2" t="inlineStr">
         <is>
           <t>9D ISLAMIAT IX</t>
@@ -6458,11 +6462,7 @@
           <t>9F URDU</t>
         </is>
       </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>7E ENGLISH</t>
-        </is>
-      </c>
+      <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
           <t>8D MATHS</t>
@@ -6497,7 +6497,11 @@
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr"/>
-      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>7E ARABIC</t>
+        </is>
+      </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
           <t>9A ISLAMIAT IX</t>
@@ -7043,7 +7047,11 @@
       </c>
       <c r="U43" s="3" t="inlineStr"/>
       <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>7D ISLAMIAT</t>
+        </is>
+      </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
           <t>8C SINDHI</t>
@@ -7109,11 +7117,7 @@
           <t>6A HISTORY</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
-        <is>
-          <t>7D SINDHI</t>
-        </is>
-      </c>
+      <c r="AS43" s="3" t="inlineStr"/>
       <c r="AT43" s="3" t="inlineStr"/>
       <c r="AU43" s="3" t="inlineStr"/>
       <c r="AV43" s="3" t="inlineStr"/>

--- a/school_timetable.xlsx
+++ b/school_timetable.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:AX44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -462,9 +462,50 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="23" customWidth="1" min="27" max="27"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="21" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="21" customWidth="1" min="36" max="36"/>
+    <col width="19" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="39" max="39"/>
+    <col width="16" customWidth="1" min="40" max="40"/>
+    <col width="18" customWidth="1" min="41" max="41"/>
+    <col width="24" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+    <col width="24" customWidth="1" min="44" max="44"/>
+    <col width="24" customWidth="1" min="45" max="45"/>
+    <col width="15" customWidth="1" min="46" max="46"/>
+    <col width="15" customWidth="1" min="47" max="47"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
+    <col width="16" customWidth="1" min="49" max="49"/>
+    <col width="14" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,6 +554,211 @@
           <t>AMINA NADEEM</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>IMRANA JUNAID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SHAZIA JAMEEL</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>SHAMA AMIR</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>HUMAIRA</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>MARYAM SHAHID</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ABDUL SALAM</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SALMAN</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>AUN NAZAMI</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>KANEEZ FATIMA</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>FARKHANDA AHMED</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>KINZA MUNEER</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>RABIA IQBAL</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>YASMEEN</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>WASEEM</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ATIQ AHMED</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>FARHANA KAMRAN</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>SARWAT AZIZ</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>BEENISH KAMRAN</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>KIRAN HUSNAIN</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>TABUSSUM</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>FARHANA ABBASI</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>FARHANA IMRAN</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>TAUQEER SABIR</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>UMME TYABA</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>IRUM NAZ</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>SAQIBA</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>KANWAL</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>FATIMA TABASSUM</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>RAFIA MEMON</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>GHAZALA</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>MARVI</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>BUSHRA JAMSHED</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>NADIA AMIR</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>ALIA</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>RUBINA AMIR</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>SAMINA ANSARI</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>LIB TEACHER</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>LUBNA TARIQ</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>KOSHILA</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>NAZAR ABBASS</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>AI TEACHER</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -556,6 +802,131 @@
           <t>9B ENGLISH</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>6C URDU</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>8B URDU</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>9D URDU</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>9C ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>6D MATHS</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>7D MATHS</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>6B MATHS</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>10A MATHS</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>10C MATHS</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>7A GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>8C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>10D PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>9A BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>10B PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>10E CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr"/>
+      <c r="AI2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>7C COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>6E S.ST</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>7B SINDHI</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr"/>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>10F SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>6A GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="AQ2" s="2" t="inlineStr"/>
+      <c r="AR2" s="2" t="inlineStr"/>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>9F ECONOMICS</t>
+        </is>
+      </c>
+      <c r="AT2" s="2" t="inlineStr"/>
+      <c r="AU2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" s="2" t="inlineStr"/>
+      <c r="AX2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr"/>
@@ -578,17 +949,146 @@
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>9D ENGLISH</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>9F ENGLISH</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>10F ENGLISH</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>9F ENGLISH</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>9D ENGLISH</t>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>8D URDU</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>6A ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>6E ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>9A ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>7C ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>7E MATHS</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>6C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>6B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>6D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>10E PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>9B BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>10B PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>9E CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>8C COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>9C COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>8B COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t>7D S.ST</t>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>10C SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>10D PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>10A PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>8A GAMES</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr"/>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>7A AI</t>
         </is>
       </c>
     </row>
@@ -622,6 +1122,139 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7A URDU</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8A URDU</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6A URDU</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7D ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>6B ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>9B ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>7B MATHS</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>6C MATHS</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>9A MATHS</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>10E MATHS</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>9D BIOLOGY</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>10B BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>10A CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>9E CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>9F GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>7E COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>9C COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AK4" s="2" t="inlineStr"/>
+      <c r="AL4" s="2" t="inlineStr"/>
+      <c r="AM4" s="2" t="inlineStr">
+        <is>
+          <t>10D SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AN4" s="2" t="inlineStr">
+        <is>
+          <t>6D SINDHI</t>
+        </is>
+      </c>
+      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AP4" s="2" t="inlineStr"/>
+      <c r="AQ4" s="2" t="inlineStr">
+        <is>
+          <t>8C MATHS</t>
+        </is>
+      </c>
+      <c r="AR4" s="2" t="inlineStr"/>
+      <c r="AS4" s="2" t="inlineStr">
+        <is>
+          <t>10F PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AT4" s="2" t="inlineStr"/>
+      <c r="AU4" s="2" t="inlineStr"/>
+      <c r="AV4" s="2" t="inlineStr">
+        <is>
+          <t>8D GAMES</t>
+        </is>
+      </c>
+      <c r="AW4" s="2" t="inlineStr">
+        <is>
+          <t>7C GAMES</t>
+        </is>
+      </c>
+      <c r="AX4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr"/>
@@ -653,6 +1286,139 @@
           <t>7C S.ST</t>
         </is>
       </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>6E URDU</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>9F URDU</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>6B URDU</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>8A ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>8B ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>9B MATHS</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>8D MATHS</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>6A MATHS</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>9A MATHS</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>9E MATHS</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>7D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>7B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>10D BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>9C PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>10A CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr">
+        <is>
+          <t>10F COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>10B SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6C SINDHI</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>7E S.ST</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>9D MATHS</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>10C PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>8C S.ST</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>7A GAMES</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr"/>
@@ -668,6 +1434,47 @@
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="Z6" s="4" t="inlineStr"/>
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AD6" s="4" t="inlineStr"/>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr"/>
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr"/>
+      <c r="AX6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr"/>
@@ -711,6 +1518,127 @@
           <t>10A ENGLISH</t>
         </is>
       </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>6D URDU</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>7B URDU</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>9E URDU</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>6A ARABIC</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>9F ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>9B MATHS</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>6E MATHS</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>7C MATHS</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>7E GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr"/>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>8A GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>10D CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>9A CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>10C COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>7D COMPUTER</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>6B HISTORY</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>8D SINDHI</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>8B GP</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>10E PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>9D MATHS</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>10F ECONOMICS</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr"/>
+      <c r="AU7" s="3" t="inlineStr"/>
+      <c r="AV7" s="3" t="inlineStr"/>
+      <c r="AW7" s="3" t="inlineStr"/>
+      <c r="AX7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
@@ -734,6 +1662,147 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>9B URDU</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8C URDU</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>9A URDU</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>8D ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>7E ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9D ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>6C ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>9E ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>7A MATHS</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>9C MATHS</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>10B MATHS</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>7C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>8B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>6E GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>10A PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>10D CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>10C CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
+          <t>9F COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>6D COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK8" s="2" t="inlineStr">
+        <is>
+          <t>6B GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="AL8" s="2" t="inlineStr">
+        <is>
+          <t>10E SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM8" s="2" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr">
+        <is>
+          <t>7D SINDHI</t>
+        </is>
+      </c>
+      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AP8" s="2" t="inlineStr"/>
+      <c r="AQ8" s="2" t="inlineStr"/>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="inlineStr"/>
+      <c r="AT8" s="2" t="inlineStr">
+        <is>
+          <t>10F LIBRARY</t>
+        </is>
+      </c>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" s="2" t="inlineStr">
+        <is>
+          <t>6A GAMES</t>
+        </is>
+      </c>
+      <c r="AX8" s="2" t="inlineStr">
+        <is>
+          <t>8A AI</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr"/>
@@ -762,9 +1831,138 @@
           <t>6B ENGLISH</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>8A Geography</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>7C URDU</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>6E ARABIC</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>6C ARABIC</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>7E PH</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>9F MATHS</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9C MATHS</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>10D MATHS</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>9D PHYSICS</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>10B MATHS</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>6A GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>10F GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>9E PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr"/>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr"/>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>10C CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>10E COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr">
+        <is>
+          <t>7A HISTORY</t>
+        </is>
+      </c>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>10A SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>8B S.ST</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>8D S.ST</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>9A LIBRARY</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr"/>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>8C GAMES</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>7B GAMES</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr"/>
@@ -800,6 +1998,135 @@
           <t>10D ENGLISH</t>
         </is>
       </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9C URDU</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7D URDU</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7E URDU</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8C ARABIC</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>7B ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>6D ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>9F MATHS</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>6E TS</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>8A MATHS</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>9D PHYSICS</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>8B MATHS</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>8D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>10A BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>10C PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>9B CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
+          <t>7A COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI10" s="2" t="inlineStr">
+        <is>
+          <t>10E COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>9E COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AP10" s="2" t="inlineStr">
+        <is>
+          <t>6C S.ST</t>
+        </is>
+      </c>
+      <c r="AQ10" s="2" t="inlineStr">
+        <is>
+          <t>10F MATHS</t>
+        </is>
+      </c>
+      <c r="AR10" s="2" t="inlineStr">
+        <is>
+          <t>10B PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr"/>
+      <c r="AX10" s="2" t="inlineStr">
+        <is>
+          <t>6B AI</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -834,11 +2161,140 @@
       </c>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>9B ENGLISH</t>
-        </is>
-      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>6C URDU</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>8B URDU</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>9D URDU</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>9B ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>6D MATHS</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>7D MATHS</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>6B MATHS</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>10A MATHS</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>7C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>7A GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>8C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>10D PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>9A BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>10B PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>10E CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr">
+        <is>
+          <t>10C COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>9C COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr">
+        <is>
+          <t>9E COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AK11" s="3" t="inlineStr">
+        <is>
+          <t>6E S.ST</t>
+        </is>
+      </c>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>7B SINDHI</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>10F SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>6A GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr"/>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>9F ECONOMICS</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr"/>
+      <c r="AU11" s="3" t="inlineStr"/>
+      <c r="AV11" s="3" t="inlineStr"/>
+      <c r="AW11" s="3" t="inlineStr"/>
+      <c r="AX11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr"/>
@@ -874,6 +2330,135 @@
           <t>10A ENGLISH</t>
         </is>
       </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>6E URDU</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>8A URDU</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8D URDU</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9A URDU</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>8C ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>9D ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>7C ARABIC</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>9C ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>6D MATHS</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>7A MATHS</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>6A MATHS</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>10D MATHS</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>8B MATHS</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>6C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>10B BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>9B PHYSICS</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr">
+        <is>
+          <t>10C COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="inlineStr">
+        <is>
+          <t>10E COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr">
+        <is>
+          <t>7D S.ST</t>
+        </is>
+      </c>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AP12" s="2" t="inlineStr">
+        <is>
+          <t>7E S.ST</t>
+        </is>
+      </c>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr">
+        <is>
+          <t>10F PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AT12" s="2" t="inlineStr">
+        <is>
+          <t>9E LIBRARY</t>
+        </is>
+      </c>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr"/>
+      <c r="AX12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr"/>
@@ -905,6 +2490,135 @@
           <t>10D ENGLISH</t>
         </is>
       </c>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>8A ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>9F ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>6C ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>7B MATHS</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>9D PHYSICS</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>10C MATHS</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>7E GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>6D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>9E PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr">
+        <is>
+          <t>10A PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>9C CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>9B CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>9A CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr">
+        <is>
+          <t>8D COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr">
+        <is>
+          <t>8B COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t>6B HISTORY</t>
+        </is>
+      </c>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>7D SINDHI</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>7C PH</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr">
+        <is>
+          <t>8C MATHS</t>
+        </is>
+      </c>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>7A GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>10F ECONOMICS</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr"/>
+      <c r="AU13" s="3" t="inlineStr"/>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>6E GAMES</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr"/>
+      <c r="AX13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr"/>
@@ -940,6 +2654,131 @@
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6D URDU</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>9B URDU</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>9F URDU</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7E URDU</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>9E ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>7A MATHS</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>6B MATHS</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>10E MATHS</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr"/>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>6A GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>6E GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>10A PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>9A CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr">
+        <is>
+          <t>6C COMPUTER</t>
+        </is>
+      </c>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>7C COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AL14" s="2" t="inlineStr">
+        <is>
+          <t>8C SINDHI</t>
+        </is>
+      </c>
+      <c r="AM14" s="2" t="inlineStr">
+        <is>
+          <t>10D SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AN14" s="2" t="inlineStr">
+        <is>
+          <t>8D SINDHI</t>
+        </is>
+      </c>
+      <c r="AO14" s="2" t="inlineStr"/>
+      <c r="AP14" s="2" t="inlineStr"/>
+      <c r="AQ14" s="2" t="inlineStr">
+        <is>
+          <t>10F MATHS</t>
+        </is>
+      </c>
+      <c r="AR14" s="2" t="inlineStr">
+        <is>
+          <t>10C PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS14" s="2" t="inlineStr"/>
+      <c r="AT14" s="2" t="inlineStr">
+        <is>
+          <t>9D LIBRARY</t>
+        </is>
+      </c>
+      <c r="AU14" s="2" t="inlineStr"/>
+      <c r="AV14" s="2" t="inlineStr">
+        <is>
+          <t>9C GAMES</t>
+        </is>
+      </c>
+      <c r="AW14" s="2" t="inlineStr"/>
+      <c r="AX14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr"/>
@@ -955,6 +2794,47 @@
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr"/>
+      <c r="O15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="inlineStr"/>
+      <c r="Q15" s="4" t="inlineStr"/>
+      <c r="R15" s="4" t="inlineStr"/>
+      <c r="S15" s="4" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr"/>
+      <c r="U15" s="4" t="inlineStr"/>
+      <c r="V15" s="4" t="inlineStr"/>
+      <c r="W15" s="4" t="inlineStr"/>
+      <c r="X15" s="4" t="inlineStr"/>
+      <c r="Y15" s="4" t="inlineStr"/>
+      <c r="Z15" s="4" t="inlineStr"/>
+      <c r="AA15" s="4" t="inlineStr"/>
+      <c r="AB15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AD15" s="4" t="inlineStr"/>
+      <c r="AE15" s="4" t="inlineStr"/>
+      <c r="AF15" s="4" t="inlineStr"/>
+      <c r="AG15" s="4" t="inlineStr"/>
+      <c r="AH15" s="4" t="inlineStr"/>
+      <c r="AI15" s="4" t="inlineStr"/>
+      <c r="AJ15" s="4" t="inlineStr"/>
+      <c r="AK15" s="4" t="inlineStr"/>
+      <c r="AL15" s="4" t="inlineStr"/>
+      <c r="AM15" s="4" t="inlineStr"/>
+      <c r="AN15" s="4" t="inlineStr"/>
+      <c r="AO15" s="4" t="inlineStr"/>
+      <c r="AP15" s="4" t="inlineStr"/>
+      <c r="AQ15" s="4" t="inlineStr"/>
+      <c r="AR15" s="4" t="inlineStr"/>
+      <c r="AS15" s="4" t="inlineStr"/>
+      <c r="AT15" s="4" t="inlineStr"/>
+      <c r="AU15" s="4" t="inlineStr"/>
+      <c r="AV15" s="4" t="inlineStr"/>
+      <c r="AW15" s="4" t="inlineStr"/>
+      <c r="AX15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr"/>
@@ -979,17 +2859,146 @@
           <t>8C ENGLISH</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7A ENGLISH</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>10F ENGLISH</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7A ENGLISH</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>7B URDU</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6A URDU</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>8D ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>9A ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>6B ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>7D PH</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6E MATHS</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>9C MATHS</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>10D MATHS</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>7C MATHS</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>9E MATHS</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>9D BIOLOGY</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>10E PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>10C PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>9B PHYSICS</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>9F GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t>7E COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="inlineStr">
+        <is>
+          <t>8A COMPUTER</t>
+        </is>
+      </c>
+      <c r="AJ16" s="2" t="inlineStr"/>
+      <c r="AK16" s="2" t="inlineStr"/>
+      <c r="AL16" s="2" t="inlineStr">
+        <is>
+          <t>10A SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM16" s="2" t="inlineStr">
+        <is>
+          <t>8B SINDHI</t>
+        </is>
+      </c>
+      <c r="AN16" s="2" t="inlineStr">
+        <is>
+          <t>6D SINDHI</t>
+        </is>
+      </c>
+      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AP16" s="2" t="inlineStr"/>
+      <c r="AQ16" s="2" t="inlineStr"/>
+      <c r="AR16" s="2" t="inlineStr">
+        <is>
+          <t>10B PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS16" s="2" t="inlineStr"/>
+      <c r="AT16" s="2" t="inlineStr"/>
+      <c r="AU16" s="2" t="inlineStr"/>
+      <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" s="2" t="inlineStr"/>
+      <c r="AX16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr"/>
@@ -1010,11 +3019,148 @@
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>9D ENGLISH</t>
+        </is>
+      </c>
       <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="3" t="inlineStr">
         <is>
           <t>7C S.ST</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>7D URDU</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>7E ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>6B ARABIC</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>9F MATHS</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>6E MATHS</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>6C MATHS</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>9A MATHS</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr"/>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>10C MATHS</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>8D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>8B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>7B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>10E PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>9B BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr">
+        <is>
+          <t>9C PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE17" s="3" t="inlineStr"/>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>10B CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr">
+        <is>
+          <t>7A COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr">
+        <is>
+          <t>10F COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>8A History</t>
+        </is>
+      </c>
+      <c r="AL17" s="3" t="inlineStr"/>
+      <c r="AM17" s="3" t="inlineStr"/>
+      <c r="AN17" s="3" t="inlineStr"/>
+      <c r="AO17" s="3" t="inlineStr"/>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>10D PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>10A PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>8C S.ST</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr"/>
+      <c r="AU17" s="3" t="inlineStr"/>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>9E GAMES</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr"/>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>6A AI</t>
         </is>
       </c>
     </row>
@@ -1051,11 +3197,136 @@
           <t>7C ENGLISH</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9D ENGLISH</t>
-        </is>
-      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>7A URDU</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>9C URDU</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>9E URDU</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>8C ARABIC</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>7B ARABIC</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>8B ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>9B MATHS</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>8D MATHS</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>8A MATHS</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>7E MATHS</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr"/>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>6B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>10A BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>10D CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="inlineStr"/>
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="2" t="inlineStr">
+        <is>
+          <t>7D COMPUTER</t>
+        </is>
+      </c>
+      <c r="AJ18" s="2" t="inlineStr">
+        <is>
+          <t>10F COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="inlineStr">
+        <is>
+          <t>6A HISTORY</t>
+        </is>
+      </c>
+      <c r="AL18" s="2" t="inlineStr">
+        <is>
+          <t>10E SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM18" s="2" t="inlineStr">
+        <is>
+          <t>10B SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AN18" s="2" t="inlineStr">
+        <is>
+          <t>6E SINDHI</t>
+        </is>
+      </c>
+      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AP18" s="2" t="inlineStr">
+        <is>
+          <t>6C S.ST</t>
+        </is>
+      </c>
+      <c r="AQ18" s="2" t="inlineStr">
+        <is>
+          <t>9D MATHS</t>
+        </is>
+      </c>
+      <c r="AR18" s="2" t="inlineStr"/>
+      <c r="AS18" s="2" t="inlineStr"/>
+      <c r="AT18" s="2" t="inlineStr"/>
+      <c r="AU18" s="2" t="inlineStr"/>
+      <c r="AV18" s="2" t="inlineStr">
+        <is>
+          <t>9F GAMES</t>
+        </is>
+      </c>
+      <c r="AW18" s="2" t="inlineStr"/>
+      <c r="AX18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr"/>
@@ -1086,7 +3357,140 @@
           <t>9E ENGLISH</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>9B ENGLISH</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>7C URDU</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>8C URDU</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>6B URDU</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>6A ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>7B ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>9F ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>7A ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="inlineStr"/>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>6C TS</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>10B MATHS</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>7D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>10F GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>10D BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr">
+        <is>
+          <t>9A PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>10A CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>9D CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>10C CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr">
+        <is>
+          <t>6D COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AM19" s="3" t="inlineStr"/>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>7E SINDHI</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>10E PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>8B S.ST</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>8D S.ST</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr"/>
+      <c r="AU19" s="3" t="inlineStr"/>
+      <c r="AV19" s="3" t="inlineStr"/>
+      <c r="AW19" s="3" t="inlineStr"/>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>8A AI</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1125,11 +3529,136 @@
           <t>9E ENGLISH</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9B ENGLISH</t>
-        </is>
-      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>6C URDU</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>8B URDU</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>9D URDU</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>9B ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>6D MATHS</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>7D MATHS</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>6B MATHS</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>10A MATHS</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr"/>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>7C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>7A GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>8C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>10D PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>9A BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>10B PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>10E CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="inlineStr">
+        <is>
+          <t>10C COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AI20" s="2" t="inlineStr">
+        <is>
+          <t>9C COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AJ20" s="2" t="inlineStr"/>
+      <c r="AK20" s="2" t="inlineStr">
+        <is>
+          <t>6E S.ST</t>
+        </is>
+      </c>
+      <c r="AL20" s="2" t="inlineStr">
+        <is>
+          <t>7B SINDHI</t>
+        </is>
+      </c>
+      <c r="AM20" s="2" t="inlineStr">
+        <is>
+          <t>10F SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AN20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AP20" s="2" t="inlineStr">
+        <is>
+          <t>6A GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="AQ20" s="2" t="inlineStr"/>
+      <c r="AR20" s="2" t="inlineStr"/>
+      <c r="AS20" s="2" t="inlineStr">
+        <is>
+          <t>9F ECONOMICS</t>
+        </is>
+      </c>
+      <c r="AT20" s="2" t="inlineStr"/>
+      <c r="AU20" s="2" t="inlineStr"/>
+      <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" s="2" t="inlineStr"/>
+      <c r="AX20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr"/>
@@ -1156,7 +3685,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>10F ENGLISH</t>
+          <t>8A Geography</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1169,6 +3698,127 @@
           <t>7C S.ST</t>
         </is>
       </c>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>7D URDU</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>8D ARABIC</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>6E ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>9D ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>9C ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t>7A MATHS</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>6A MATHS</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>9A MATHS</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr"/>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>9E MATHS</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr"/>
+      <c r="AA21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr"/>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>9B BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr"/>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>10D CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>10E CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr">
+        <is>
+          <t>7E COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr">
+        <is>
+          <t>6B GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>8C SINDHI</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr"/>
+      <c r="AN21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr"/>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>6C S.ST</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr">
+        <is>
+          <t>10F MATHS</t>
+        </is>
+      </c>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>8B S.ST</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr"/>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>10B LIBRARY</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr"/>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>10C GAMES</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr"/>
+      <c r="AX21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr"/>
@@ -1204,6 +3854,135 @@
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>7A URDU</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>7B URDU</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>7E URDU</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>8A ARABIC</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>6D ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>8B ARABIC</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>9F MATHS</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>6A MATHS</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>10D MATHS</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>9D PHYSICS</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr"/>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>8D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>7D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>6E GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>9A PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
+          <t>10A CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="inlineStr">
+        <is>
+          <t>9B PHYSICS</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr">
+        <is>
+          <t>9E COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="inlineStr"/>
+      <c r="AL22" s="2" t="inlineStr"/>
+      <c r="AM22" s="2" t="inlineStr"/>
+      <c r="AN22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>8C GP</t>
+        </is>
+      </c>
+      <c r="AP22" s="2" t="inlineStr"/>
+      <c r="AQ22" s="2" t="inlineStr"/>
+      <c r="AR22" s="2" t="inlineStr">
+        <is>
+          <t>10C PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS22" s="2" t="inlineStr">
+        <is>
+          <t>10F PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AT22" s="2" t="inlineStr">
+        <is>
+          <t>10E LIBRARY</t>
+        </is>
+      </c>
+      <c r="AU22" s="2" t="inlineStr"/>
+      <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" s="2" t="inlineStr">
+        <is>
+          <t>6C GAMES</t>
+        </is>
+      </c>
+      <c r="AX22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr"/>
@@ -1229,6 +4008,143 @@
       <c r="I23" s="3" t="inlineStr">
         <is>
           <t>10A ENGLISH</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>6E URDU</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>8A URDU</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>9F URDU</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>6A URDU</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>9A ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>7A ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr">
+        <is>
+          <t>8D MATHS</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr"/>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>10E MATHS</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>8B MATHS</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>6C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr"/>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>7B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr"/>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>10B BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>9C CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>9B PHYSICS</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr"/>
+      <c r="AH23" s="3" t="inlineStr">
+        <is>
+          <t>8C COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr">
+        <is>
+          <t>9E COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AK23" s="3" t="inlineStr">
+        <is>
+          <t>7D S.ST</t>
+        </is>
+      </c>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>10C SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>10D SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>7C SINDHI</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr"/>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>7E S.ST</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr">
+        <is>
+          <t>9D MATHS</t>
+        </is>
+      </c>
+      <c r="AR23" s="3" t="inlineStr"/>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>10F ECONOMICS</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr"/>
+      <c r="AU23" s="3" t="inlineStr"/>
+      <c r="AV23" s="3" t="inlineStr"/>
+      <c r="AW23" s="3" t="inlineStr"/>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>6B AI</t>
         </is>
       </c>
     </row>
@@ -1246,6 +4162,47 @@
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="4" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr"/>
+      <c r="P24" s="4" t="inlineStr"/>
+      <c r="Q24" s="4" t="inlineStr"/>
+      <c r="R24" s="4" t="inlineStr"/>
+      <c r="S24" s="4" t="inlineStr"/>
+      <c r="T24" s="4" t="inlineStr"/>
+      <c r="U24" s="4" t="inlineStr"/>
+      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" s="4" t="inlineStr"/>
+      <c r="X24" s="4" t="inlineStr"/>
+      <c r="Y24" s="4" t="inlineStr"/>
+      <c r="Z24" s="4" t="inlineStr"/>
+      <c r="AA24" s="4" t="inlineStr"/>
+      <c r="AB24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AD24" s="4" t="inlineStr"/>
+      <c r="AE24" s="4" t="inlineStr"/>
+      <c r="AF24" s="4" t="inlineStr"/>
+      <c r="AG24" s="4" t="inlineStr"/>
+      <c r="AH24" s="4" t="inlineStr"/>
+      <c r="AI24" s="4" t="inlineStr"/>
+      <c r="AJ24" s="4" t="inlineStr"/>
+      <c r="AK24" s="4" t="inlineStr"/>
+      <c r="AL24" s="4" t="inlineStr"/>
+      <c r="AM24" s="4" t="inlineStr"/>
+      <c r="AN24" s="4" t="inlineStr"/>
+      <c r="AO24" s="4" t="inlineStr"/>
+      <c r="AP24" s="4" t="inlineStr"/>
+      <c r="AQ24" s="4" t="inlineStr"/>
+      <c r="AR24" s="4" t="inlineStr"/>
+      <c r="AS24" s="4" t="inlineStr"/>
+      <c r="AT24" s="4" t="inlineStr"/>
+      <c r="AU24" s="4" t="inlineStr"/>
+      <c r="AV24" s="4" t="inlineStr"/>
+      <c r="AW24" s="4" t="inlineStr"/>
+      <c r="AX24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr"/>
@@ -1280,7 +4237,136 @@
           <t>7A ENGLISH</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>10F ENGLISH</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>6D URDU</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>9C URDU</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>9E URDU</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>7D ARABIC</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>7B ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr"/>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>9B MATHS</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>8A MATHS</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr"/>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>8B MATHS</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>6B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr"/>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>10E PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>10D BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr"/>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>9D CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>9F GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>6E COMPUTER</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr">
+        <is>
+          <t>7C COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK25" s="3" t="inlineStr">
+        <is>
+          <t>6A HISTORY</t>
+        </is>
+      </c>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>10A SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr"/>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6C SINDHI</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>8D GP</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>10B PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr"/>
+      <c r="AT25" s="3" t="inlineStr"/>
+      <c r="AU25" s="3" t="inlineStr"/>
+      <c r="AV25" s="3" t="inlineStr"/>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>7E GAMES</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr"/>
@@ -1301,7 +4387,11 @@
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>9D ENGLISH</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>8B ENGLISH</t>
@@ -1309,9 +4399,138 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9D ENGLISH</t>
-        </is>
-      </c>
+          <t>9B ENGLISH</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>7C URDU</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>8D ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>6E ARABIC</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6B ARABIC</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>7D MATHS</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>9C MATHS</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>8A MATHS</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr"/>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>7E GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>6A GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>10A PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr">
+        <is>
+          <t>9E CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr">
+        <is>
+          <t>9F COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AI26" s="2" t="inlineStr">
+        <is>
+          <t>6C COMPUTER</t>
+        </is>
+      </c>
+      <c r="AJ26" s="2" t="inlineStr"/>
+      <c r="AK26" s="2" t="inlineStr">
+        <is>
+          <t>7A HISTORY</t>
+        </is>
+      </c>
+      <c r="AL26" s="2" t="inlineStr">
+        <is>
+          <t>10C SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM26" s="2" t="inlineStr">
+        <is>
+          <t>10B SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AN26" s="2" t="inlineStr">
+        <is>
+          <t>6D SINDHI</t>
+        </is>
+      </c>
+      <c r="AO26" s="2" t="inlineStr"/>
+      <c r="AP26" s="2" t="inlineStr">
+        <is>
+          <t>10E PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AQ26" s="2" t="inlineStr">
+        <is>
+          <t>10F MATHS</t>
+        </is>
+      </c>
+      <c r="AR26" s="2" t="inlineStr"/>
+      <c r="AS26" s="2" t="inlineStr">
+        <is>
+          <t>8C S.ST</t>
+        </is>
+      </c>
+      <c r="AT26" s="2" t="inlineStr">
+        <is>
+          <t>10D LIBRARY</t>
+        </is>
+      </c>
+      <c r="AU26" s="2" t="inlineStr"/>
+      <c r="AV26" s="2" t="inlineStr">
+        <is>
+          <t>9A GAMES</t>
+        </is>
+      </c>
+      <c r="AW26" s="2" t="inlineStr"/>
+      <c r="AX26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr"/>
@@ -1347,6 +4566,127 @@
           <t>10D ENGLISH</t>
         </is>
       </c>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>9B URDU</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>8C URDU</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>9A URDU</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>7D ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>9F ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>7C ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr"/>
+      <c r="V27" s="3" t="inlineStr"/>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>7E MATHS</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>10C MATHS</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>9D BIOLOGY</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>6D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>9E PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr"/>
+      <c r="AD27" s="3" t="inlineStr">
+        <is>
+          <t>9C PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE27" s="3" t="inlineStr"/>
+      <c r="AF27" s="3" t="inlineStr"/>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>10B CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr">
+        <is>
+          <t>7A COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr">
+        <is>
+          <t>7B COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>10E SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr"/>
+      <c r="AN27" s="3" t="inlineStr"/>
+      <c r="AO27" s="3" t="inlineStr"/>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>10A PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>8D S.ST</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr"/>
+      <c r="AU27" s="3" t="inlineStr"/>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>8B GAMES</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>6B GAMES</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr"/>
@@ -1378,6 +4718,139 @@
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>8D URDU</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>6B URDU</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>9E ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>7B MATHS</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>6E MATHS</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>6C MATHS</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>7C MATHS</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>10B MATHS</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>9D BIOLOGY</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>8B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>10F GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>10A BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>9C PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr">
+        <is>
+          <t>9B CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="inlineStr">
+        <is>
+          <t>9A CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="inlineStr">
+        <is>
+          <t>6A COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr">
+        <is>
+          <t>6D COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="inlineStr">
+        <is>
+          <t>8A History</t>
+        </is>
+      </c>
+      <c r="AL28" s="2" t="inlineStr"/>
+      <c r="AM28" s="2" t="inlineStr"/>
+      <c r="AN28" s="2" t="inlineStr">
+        <is>
+          <t>7E SINDHI</t>
+        </is>
+      </c>
+      <c r="AO28" s="2" t="inlineStr"/>
+      <c r="AP28" s="2" t="inlineStr">
+        <is>
+          <t>10D PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AQ28" s="2" t="inlineStr">
+        <is>
+          <t>8C MATHS</t>
+        </is>
+      </c>
+      <c r="AR28" s="2" t="inlineStr"/>
+      <c r="AS28" s="2" t="inlineStr"/>
+      <c r="AT28" s="2" t="inlineStr">
+        <is>
+          <t>10C LIBRARY</t>
+        </is>
+      </c>
+      <c r="AU28" s="2" t="inlineStr"/>
+      <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" s="2" t="inlineStr"/>
+      <c r="AX28" s="2" t="inlineStr">
+        <is>
+          <t>7A AI</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1421,6 +4894,131 @@
           <t>9B ENGLISH</t>
         </is>
       </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>6C URDU</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>8B URDU</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>9D URDU</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>6A ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>6D MATHS</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr">
+        <is>
+          <t>7D MATHS</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>6B MATHS</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>10A MATHS</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr"/>
+      <c r="X29" s="3" t="inlineStr"/>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>7C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>7A GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>8C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>10D PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>9A BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr">
+        <is>
+          <t>10B PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE29" s="3" t="inlineStr"/>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>10E CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr">
+        <is>
+          <t>10C COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>9C COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr">
+        <is>
+          <t>7B COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>6E S.ST</t>
+        </is>
+      </c>
+      <c r="AL29" s="3" t="inlineStr"/>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>10F SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr"/>
+      <c r="AO29" s="3" t="inlineStr"/>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr"/>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>9F ECONOMICS</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr"/>
+      <c r="AU29" s="3" t="inlineStr"/>
+      <c r="AV29" s="3" t="inlineStr"/>
+      <c r="AW29" s="3" t="inlineStr"/>
+      <c r="AX29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr"/>
@@ -1447,11 +5045,144 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>8A Geography</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
           <t>10F ENGLISH</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>6D URDU</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>7B URDU</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>7D URDU</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>7E ARABIC</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>9D ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>6B ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>9B MATHS</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>7A MATHS</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>6A MATHS</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>10A MATHS</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>7C MATHS</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>10B MATHS</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>10D PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>9A BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>10C PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr">
+        <is>
+          <t>9E CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr">
+        <is>
+          <t>10E COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AJ30" s="2" t="inlineStr">
+        <is>
+          <t>8B COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="inlineStr"/>
+      <c r="AL30" s="2" t="inlineStr"/>
+      <c r="AM30" s="2" t="inlineStr"/>
+      <c r="AN30" s="2" t="inlineStr">
+        <is>
+          <t>8D SINDHI</t>
+        </is>
+      </c>
+      <c r="AO30" s="2" t="inlineStr"/>
+      <c r="AP30" s="2" t="inlineStr">
+        <is>
+          <t>6C S.ST</t>
+        </is>
+      </c>
+      <c r="AQ30" s="2" t="inlineStr"/>
+      <c r="AR30" s="2" t="inlineStr"/>
+      <c r="AS30" s="2" t="inlineStr">
+        <is>
+          <t>8C S.ST</t>
+        </is>
+      </c>
+      <c r="AT30" s="2" t="inlineStr">
+        <is>
+          <t>9F LIBRARY</t>
+        </is>
+      </c>
+      <c r="AU30" s="2" t="inlineStr"/>
+      <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" s="2" t="inlineStr"/>
+      <c r="AX30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr"/>
@@ -1474,9 +5205,146 @@
           <t>8B ENGLISH</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>10D ENGLISH</t>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>8A URDU</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>6B URDU</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>8C ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>7B ARABIC</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>7A ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>9E ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>9F MATHS</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr"/>
+      <c r="V31" s="3" t="inlineStr"/>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>7C MATHS</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr"/>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>6C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>7D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>6D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>10E PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>10D BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr">
+        <is>
+          <t>10C PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>9C CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>9B CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>9A CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr">
+        <is>
+          <t>8D COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr"/>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>10B SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6E SINDHI</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr"/>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>7E S.ST</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr">
+        <is>
+          <t>10F MATHS</t>
+        </is>
+      </c>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>10A PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr"/>
+      <c r="AT31" s="3" t="inlineStr"/>
+      <c r="AU31" s="3" t="inlineStr"/>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>9D GAMES</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr"/>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>6A AI</t>
         </is>
       </c>
     </row>
@@ -1518,6 +5386,131 @@
           <t>7C S.ST</t>
         </is>
       </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>9F URDU</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>8A ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>6D ARABIC</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>9C ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>7E MATHS</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>9E MATHS</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>8D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>8B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>6E GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr">
+        <is>
+          <t>9B CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>10C CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH32" s="2" t="inlineStr">
+        <is>
+          <t>6A COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI32" s="2" t="inlineStr">
+        <is>
+          <t>7D COMPUTER</t>
+        </is>
+      </c>
+      <c r="AJ32" s="2" t="inlineStr">
+        <is>
+          <t>6B COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="inlineStr"/>
+      <c r="AL32" s="2" t="inlineStr">
+        <is>
+          <t>10E SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM32" s="2" t="inlineStr">
+        <is>
+          <t>10D SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AN32" s="2" t="inlineStr">
+        <is>
+          <t>6C SINDHI</t>
+        </is>
+      </c>
+      <c r="AO32" s="2" t="inlineStr"/>
+      <c r="AP32" s="2" t="inlineStr"/>
+      <c r="AQ32" s="2" t="inlineStr">
+        <is>
+          <t>9D MATHS</t>
+        </is>
+      </c>
+      <c r="AR32" s="2" t="inlineStr">
+        <is>
+          <t>10B PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS32" s="2" t="inlineStr">
+        <is>
+          <t>10F ECONOMICS</t>
+        </is>
+      </c>
+      <c r="AT32" s="2" t="inlineStr"/>
+      <c r="AU32" s="2" t="inlineStr"/>
+      <c r="AV32" s="2" t="inlineStr">
+        <is>
+          <t>10A GAMES</t>
+        </is>
+      </c>
+      <c r="AW32" s="2" t="inlineStr"/>
+      <c r="AX32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr"/>
@@ -1533,6 +5526,47 @@
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr"/>
       <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="inlineStr"/>
+      <c r="P33" s="4" t="inlineStr"/>
+      <c r="Q33" s="4" t="inlineStr"/>
+      <c r="R33" s="4" t="inlineStr"/>
+      <c r="S33" s="4" t="inlineStr"/>
+      <c r="T33" s="4" t="inlineStr"/>
+      <c r="U33" s="4" t="inlineStr"/>
+      <c r="V33" s="4" t="inlineStr"/>
+      <c r="W33" s="4" t="inlineStr"/>
+      <c r="X33" s="4" t="inlineStr"/>
+      <c r="Y33" s="4" t="inlineStr"/>
+      <c r="Z33" s="4" t="inlineStr"/>
+      <c r="AA33" s="4" t="inlineStr"/>
+      <c r="AB33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AD33" s="4" t="inlineStr"/>
+      <c r="AE33" s="4" t="inlineStr"/>
+      <c r="AF33" s="4" t="inlineStr"/>
+      <c r="AG33" s="4" t="inlineStr"/>
+      <c r="AH33" s="4" t="inlineStr"/>
+      <c r="AI33" s="4" t="inlineStr"/>
+      <c r="AJ33" s="4" t="inlineStr"/>
+      <c r="AK33" s="4" t="inlineStr"/>
+      <c r="AL33" s="4" t="inlineStr"/>
+      <c r="AM33" s="4" t="inlineStr"/>
+      <c r="AN33" s="4" t="inlineStr"/>
+      <c r="AO33" s="4" t="inlineStr"/>
+      <c r="AP33" s="4" t="inlineStr"/>
+      <c r="AQ33" s="4" t="inlineStr"/>
+      <c r="AR33" s="4" t="inlineStr"/>
+      <c r="AS33" s="4" t="inlineStr"/>
+      <c r="AT33" s="4" t="inlineStr"/>
+      <c r="AU33" s="4" t="inlineStr"/>
+      <c r="AV33" s="4" t="inlineStr"/>
+      <c r="AW33" s="4" t="inlineStr"/>
+      <c r="AX33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr"/>
@@ -1571,7 +5605,132 @@
           <t>7C ENGLISH</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>10D ENGLISH</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>7A URDU</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>9B URDU</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>6A ARABIC</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>9C MATHS</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>8A MATHS</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>7E MATHS</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>9E MATHS</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>9D BIOLOGY</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>6B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>9A PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>9F GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AH34" s="2" t="inlineStr">
+        <is>
+          <t>8C COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI34" s="2" t="inlineStr">
+        <is>
+          <t>6E COMPUTER</t>
+        </is>
+      </c>
+      <c r="AJ34" s="2" t="inlineStr">
+        <is>
+          <t>10F COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AK34" s="2" t="inlineStr">
+        <is>
+          <t>7D S.ST</t>
+        </is>
+      </c>
+      <c r="AL34" s="2" t="inlineStr">
+        <is>
+          <t>10A SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM34" s="2" t="inlineStr"/>
+      <c r="AN34" s="2" t="inlineStr"/>
+      <c r="AO34" s="2" t="inlineStr"/>
+      <c r="AP34" s="2" t="inlineStr">
+        <is>
+          <t>10E PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AQ34" s="2" t="inlineStr"/>
+      <c r="AR34" s="2" t="inlineStr">
+        <is>
+          <t>8B S.ST</t>
+        </is>
+      </c>
+      <c r="AS34" s="2" t="inlineStr">
+        <is>
+          <t>8D S.ST</t>
+        </is>
+      </c>
+      <c r="AT34" s="2" t="inlineStr"/>
+      <c r="AU34" s="2" t="inlineStr"/>
+      <c r="AV34" s="2" t="inlineStr"/>
+      <c r="AW34" s="2" t="inlineStr">
+        <is>
+          <t>6D GAMES</t>
+        </is>
+      </c>
+      <c r="AX34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr"/>
@@ -1603,6 +5762,139 @@
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>8C URDU</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>7E URDU</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>8D ARABIC</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>6D ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>7A ARABIC</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>9B ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>7B MATHS</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t>6E MATHS</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>6C MATHS</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>9A MATHS</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr"/>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>10C MATHS</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>10F GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>9E PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>10B BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr">
+        <is>
+          <t>9C PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>10A CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>9D CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr"/>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>8A COMPUTER</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr">
+        <is>
+          <t>6B COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr"/>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>8B SINDHI</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>7C SINDHI</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr"/>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>10D PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr"/>
+      <c r="AS35" s="3" t="inlineStr"/>
+      <c r="AT35" s="3" t="inlineStr"/>
+      <c r="AU35" s="3" t="inlineStr"/>
+      <c r="AV35" s="3" t="inlineStr"/>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>7D GAMES</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr"/>
@@ -1630,6 +5922,139 @@
           <t>10A ENGLISH</t>
         </is>
       </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>6E URDU</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>8D URDU</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>6A URDU</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>9A ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>7C ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>8B ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>7B MATHS</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>6C MATHS</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>10E MATHS</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr"/>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>7E GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>10F GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>9E PHYSICS</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>9B BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr">
+        <is>
+          <t>9D CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="inlineStr">
+        <is>
+          <t>10B CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH36" s="2" t="inlineStr">
+        <is>
+          <t>9F COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+      <c r="AK36" s="2" t="inlineStr">
+        <is>
+          <t>6B HISTORY</t>
+        </is>
+      </c>
+      <c r="AL36" s="2" t="inlineStr">
+        <is>
+          <t>10C SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM36" s="2" t="inlineStr"/>
+      <c r="AN36" s="2" t="inlineStr">
+        <is>
+          <t>7D SINDHI</t>
+        </is>
+      </c>
+      <c r="AO36" s="2" t="inlineStr"/>
+      <c r="AP36" s="2" t="inlineStr"/>
+      <c r="AQ36" s="2" t="inlineStr">
+        <is>
+          <t>8C MATHS</t>
+        </is>
+      </c>
+      <c r="AR36" s="2" t="inlineStr">
+        <is>
+          <t>7A GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="AS36" s="2" t="inlineStr"/>
+      <c r="AT36" s="2" t="inlineStr">
+        <is>
+          <t>9C LIBRARY</t>
+        </is>
+      </c>
+      <c r="AU36" s="2" t="inlineStr"/>
+      <c r="AV36" s="2" t="inlineStr">
+        <is>
+          <t>10D GAMES</t>
+        </is>
+      </c>
+      <c r="AW36" s="2" t="inlineStr"/>
+      <c r="AX36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr"/>
@@ -1658,13 +6083,142 @@
           <t>6B ENGLISH</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>9D ENGLISH</t>
+        </is>
+      </c>
       <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>9D ENGLISH</t>
-        </is>
-      </c>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>7C URDU</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>9C URDU</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>9E URDU</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>9A URDU</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>8A ARABIC</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>6E ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>6C ARABIC</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr"/>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t>8D MATHS</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr"/>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>10D MATHS</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>10E MATHS</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>8B MATHS</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>6A GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>7B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr"/>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>9B BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr">
+        <is>
+          <t>10A PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE37" s="3" t="inlineStr"/>
+      <c r="AF37" s="3" t="inlineStr"/>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>10B CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr">
+        <is>
+          <t>9F COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AI37" s="3" t="inlineStr"/>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr">
+        <is>
+          <t>7A HISTORY</t>
+        </is>
+      </c>
+      <c r="AL37" s="3" t="inlineStr"/>
+      <c r="AM37" s="3" t="inlineStr"/>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>7E SINDHI</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr"/>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr">
+        <is>
+          <t>8C MATHS</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>10C PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>10F PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr"/>
+      <c r="AU37" s="3" t="inlineStr"/>
+      <c r="AV37" s="3" t="inlineStr"/>
+      <c r="AW37" s="3" t="inlineStr"/>
+      <c r="AX37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1699,11 +6253,140 @@
           <t>9E ENGLISH</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>9B ENGLISH</t>
-        </is>
-      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>7C URDU</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>9C URDU</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>8C URDU</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>9A URDU</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>9D ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>7A ARABIC</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>9B ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>6D MATHS</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>8D MATHS</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>6C MATHS</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>10A MATHS</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>10B MATHS</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>7D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>10D BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr">
+        <is>
+          <t>6A COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI38" s="2" t="inlineStr">
+        <is>
+          <t>8A COMPUTER</t>
+        </is>
+      </c>
+      <c r="AJ38" s="2" t="inlineStr"/>
+      <c r="AK38" s="2" t="inlineStr">
+        <is>
+          <t>6B GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="AL38" s="2" t="inlineStr">
+        <is>
+          <t>10E SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM38" s="2" t="inlineStr">
+        <is>
+          <t>8B SINDHI</t>
+        </is>
+      </c>
+      <c r="AN38" s="2" t="inlineStr">
+        <is>
+          <t>6E SINDHI</t>
+        </is>
+      </c>
+      <c r="AO38" s="2" t="inlineStr"/>
+      <c r="AP38" s="2" t="inlineStr">
+        <is>
+          <t>7B PH</t>
+        </is>
+      </c>
+      <c r="AQ38" s="2" t="inlineStr">
+        <is>
+          <t>10F MATHS</t>
+        </is>
+      </c>
+      <c r="AR38" s="2" t="inlineStr"/>
+      <c r="AS38" s="2" t="inlineStr">
+        <is>
+          <t>9F ECONOMICS</t>
+        </is>
+      </c>
+      <c r="AT38" s="2" t="inlineStr"/>
+      <c r="AU38" s="2" t="inlineStr"/>
+      <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" s="2" t="inlineStr"/>
+      <c r="AX38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr"/>
@@ -1731,6 +6414,143 @@
       </c>
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>9B URDU</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>9F URDU</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>6A URDU</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>7D ARABIC</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>7E ARABIC</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>9A ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>8B ARABIC</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>9C ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>6D TS</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t>8D MATHS</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="inlineStr"/>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>9D PHYSICS</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>9E MATHS</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>7C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>7A GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>7B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr"/>
+      <c r="AC39" s="3" t="inlineStr"/>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr"/>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>10D CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>10C CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>6E COMPUTER</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr">
+        <is>
+          <t>6B COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>8A History</t>
+        </is>
+      </c>
+      <c r="AL39" s="3" t="inlineStr"/>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>10F SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr"/>
+      <c r="AO39" s="3" t="inlineStr"/>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr">
+        <is>
+          <t>8C MATHS</t>
+        </is>
+      </c>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>10B PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr"/>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>10A LIBRARY</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr"/>
+      <c r="AV39" s="3" t="inlineStr"/>
+      <c r="AW39" s="3" t="inlineStr"/>
+      <c r="AX39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr"/>
@@ -1774,6 +6594,123 @@
           <t>10A ENGLISH</t>
         </is>
       </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>6D URDU</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>9D URDU</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>8C ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>9F ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>6C ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>9B MATHS</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>6A MATHS</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>7E MATHS</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>10C MATHS</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>8B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>6E GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr">
+        <is>
+          <t>9C CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr">
+        <is>
+          <t>10B CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AH40" s="2" t="inlineStr">
+        <is>
+          <t>8D COMPUTER</t>
+        </is>
+      </c>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr">
+        <is>
+          <t>9E COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AK40" s="2" t="inlineStr"/>
+      <c r="AL40" s="2" t="inlineStr"/>
+      <c r="AM40" s="2" t="inlineStr"/>
+      <c r="AN40" s="2" t="inlineStr"/>
+      <c r="AO40" s="2" t="inlineStr"/>
+      <c r="AP40" s="2" t="inlineStr">
+        <is>
+          <t>10D PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AQ40" s="2" t="inlineStr"/>
+      <c r="AR40" s="2" t="inlineStr">
+        <is>
+          <t>7A GEOGRAPHY</t>
+        </is>
+      </c>
+      <c r="AS40" s="2" t="inlineStr">
+        <is>
+          <t>10F PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AT40" s="2" t="inlineStr"/>
+      <c r="AU40" s="2" t="inlineStr"/>
+      <c r="AV40" s="2" t="inlineStr">
+        <is>
+          <t>10E GAMES</t>
+        </is>
+      </c>
+      <c r="AW40" s="2" t="inlineStr"/>
+      <c r="AX40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr"/>
@@ -1814,9 +6751,130 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>9D ENGLISH</t>
-        </is>
-      </c>
+          <t>9B ENGLISH</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>7A URDU</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>8A URDU</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>8D URDU</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>9E ISLAMIAT IX</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t>7D MATHS</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>6B MATHS</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>9A MATHS</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>10E MATHS</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr"/>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>7E GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>8C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr"/>
+      <c r="AC41" s="3" t="inlineStr"/>
+      <c r="AD41" s="3" t="inlineStr">
+        <is>
+          <t>10C PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>9C CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr"/>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>9F GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>6C COMPUTER</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr">
+        <is>
+          <t>7B COMPUTER</t>
+        </is>
+      </c>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>10A SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>10D SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>7C SINDHI</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr"/>
+      <c r="AP41" s="3" t="inlineStr"/>
+      <c r="AQ41" s="3" t="inlineStr">
+        <is>
+          <t>9D MATHS</t>
+        </is>
+      </c>
+      <c r="AR41" s="3" t="inlineStr"/>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>10F ECONOMICS</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr"/>
+      <c r="AU41" s="3" t="inlineStr"/>
+      <c r="AV41" s="3" t="inlineStr"/>
+      <c r="AW41" s="3" t="inlineStr"/>
+      <c r="AX41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr"/>
@@ -1832,6 +6890,47 @@
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr"/>
+      <c r="P42" s="4" t="inlineStr"/>
+      <c r="Q42" s="4" t="inlineStr"/>
+      <c r="R42" s="4" t="inlineStr"/>
+      <c r="S42" s="4" t="inlineStr"/>
+      <c r="T42" s="4" t="inlineStr"/>
+      <c r="U42" s="4" t="inlineStr"/>
+      <c r="V42" s="4" t="inlineStr"/>
+      <c r="W42" s="4" t="inlineStr"/>
+      <c r="X42" s="4" t="inlineStr"/>
+      <c r="Y42" s="4" t="inlineStr"/>
+      <c r="Z42" s="4" t="inlineStr"/>
+      <c r="AA42" s="4" t="inlineStr"/>
+      <c r="AB42" s="4" t="inlineStr"/>
+      <c r="AC42" s="4" t="inlineStr"/>
+      <c r="AD42" s="4" t="inlineStr"/>
+      <c r="AE42" s="4" t="inlineStr"/>
+      <c r="AF42" s="4" t="inlineStr"/>
+      <c r="AG42" s="4" t="inlineStr"/>
+      <c r="AH42" s="4" t="inlineStr"/>
+      <c r="AI42" s="4" t="inlineStr"/>
+      <c r="AJ42" s="4" t="inlineStr"/>
+      <c r="AK42" s="4" t="inlineStr"/>
+      <c r="AL42" s="4" t="inlineStr"/>
+      <c r="AM42" s="4" t="inlineStr"/>
+      <c r="AN42" s="4" t="inlineStr"/>
+      <c r="AO42" s="4" t="inlineStr"/>
+      <c r="AP42" s="4" t="inlineStr"/>
+      <c r="AQ42" s="4" t="inlineStr"/>
+      <c r="AR42" s="4" t="inlineStr"/>
+      <c r="AS42" s="4" t="inlineStr"/>
+      <c r="AT42" s="4" t="inlineStr"/>
+      <c r="AU42" s="4" t="inlineStr"/>
+      <c r="AV42" s="4" t="inlineStr"/>
+      <c r="AW42" s="4" t="inlineStr"/>
+      <c r="AX42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr"/>
@@ -1858,7 +6957,144 @@
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>10F ENGLISH</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>6E URDU</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>7B URDU</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>9E URDU</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>7E URDU</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>7D ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>9F MATHS</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t>7A MATHS</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9C MATHS</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>10D MATHS</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>7C MATHS</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>8B MATHS</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>6C GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>6B GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>6D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr"/>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>10A BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr">
+        <is>
+          <t>9A PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE43" s="3" t="inlineStr"/>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>9D CHEMISTRY</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr"/>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr"/>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr">
+        <is>
+          <t>6A HISTORY</t>
+        </is>
+      </c>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>8C SINDHI</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>10B SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr"/>
+      <c r="AO43" s="3" t="inlineStr"/>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>10E PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>10C PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr"/>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>9B LIBRARY</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr"/>
+      <c r="AV43" s="3" t="inlineStr"/>
+      <c r="AW43" s="3" t="inlineStr"/>
+      <c r="AX43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr"/>
@@ -1885,7 +7121,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>10F ENGLISH</t>
+          <t>9D ENGLISH</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1898,6 +7134,127 @@
           <t>10D ENGLISH</t>
         </is>
       </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>6C URDU</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>8B URDU</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>7D URDU</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>6B URDU</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>7E ISLAMIAT</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>6D ARABIC</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>7C ARABIC</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>7B MATHS</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>6E MATHS</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>8A MATHS</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr"/>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>8D GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>6A GENERAL SCIENCE</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>10B BIOLOGY</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>9A PHYSICS</t>
+        </is>
+      </c>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr">
+        <is>
+          <t>9B PHYSICS</t>
+        </is>
+      </c>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr">
+        <is>
+          <t>9F COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AI44" s="2" t="inlineStr">
+        <is>
+          <t>10E COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AJ44" s="2" t="inlineStr">
+        <is>
+          <t>10F COMPUTER IX-X</t>
+        </is>
+      </c>
+      <c r="AK44" s="2" t="inlineStr"/>
+      <c r="AL44" s="2" t="inlineStr">
+        <is>
+          <t>10C SINDHI-X</t>
+        </is>
+      </c>
+      <c r="AM44" s="2" t="inlineStr"/>
+      <c r="AN44" s="2" t="inlineStr"/>
+      <c r="AO44" s="2" t="inlineStr"/>
+      <c r="AP44" s="2" t="inlineStr"/>
+      <c r="AQ44" s="2" t="inlineStr"/>
+      <c r="AR44" s="2" t="inlineStr">
+        <is>
+          <t>10A PAKISTAN STUDIES</t>
+        </is>
+      </c>
+      <c r="AS44" s="2" t="inlineStr"/>
+      <c r="AT44" s="2" t="inlineStr"/>
+      <c r="AU44" s="2" t="inlineStr"/>
+      <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" s="2" t="inlineStr"/>
+      <c r="AX44" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/school_timetable.xlsx
+++ b/school_timetable.xlsx
@@ -1115,7 +1115,11 @@
           <t>6E ENGLISH</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10B ENGLISH</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8B ENGLISH</t>
@@ -1185,11 +1189,7 @@
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="inlineStr"/>
       <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>10B BIOLOGY</t>
-        </is>
-      </c>
+      <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="inlineStr">
         <is>
@@ -1377,7 +1377,11 @@
           <t>10F COMPUTER IX-X</t>
         </is>
       </c>
-      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>7A HISTORY</t>
+        </is>
+      </c>
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr">
         <is>
@@ -1413,11 +1417,7 @@
       <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="inlineStr"/>
       <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
-        <is>
-          <t>7A GAMES</t>
-        </is>
-      </c>
+      <c r="AW5" s="3" t="inlineStr"/>
       <c r="AX5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1500,14 +1500,10 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>8C ENGLISH</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>10B ENGLISH</t>
-        </is>
-      </c>
+          <t>6B ENGLISH</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>7A ENGLISH</t>
@@ -1573,7 +1569,11 @@
       <c r="Z7" s="3" t="inlineStr"/>
       <c r="AA7" s="3" t="inlineStr"/>
       <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>10B BIOLOGY</t>
+        </is>
+      </c>
       <c r="AD7" s="3" t="inlineStr"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
@@ -1601,11 +1601,7 @@
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr">
-        <is>
-          <t>6B HISTORY</t>
-        </is>
-      </c>
+      <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr">
@@ -1636,7 +1632,11 @@
       </c>
       <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>8C GAMES</t>
+        </is>
+      </c>
       <c r="AW7" s="3" t="inlineStr"/>
       <c r="AX7" s="3" t="inlineStr"/>
     </row>
@@ -1818,17 +1818,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
+          <t>8C ENGLISH</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>6D S.ST</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
           <t>7D ENGLISH</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>6D S.ST</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>6B ENGLISH</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1905,7 +1905,11 @@
           <t>9E PHYSICS</t>
         </is>
       </c>
-      <c r="AC9" s="3" t="inlineStr"/>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>9B BIOLOGY</t>
+        </is>
+      </c>
       <c r="AD9" s="3" t="inlineStr"/>
       <c r="AE9" s="3" t="inlineStr"/>
       <c r="AF9" s="3" t="inlineStr"/>
@@ -1923,7 +1927,7 @@
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr">
         <is>
-          <t>7A HISTORY</t>
+          <t>6B HISTORY</t>
         </is>
       </c>
       <c r="AL9" s="3" t="inlineStr">
@@ -1952,14 +1956,10 @@
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>8C GAMES</t>
-        </is>
-      </c>
+      <c r="AV9" s="3" t="inlineStr"/>
       <c r="AW9" s="3" t="inlineStr">
         <is>
-          <t>7B GAMES</t>
+          <t>7A GAMES</t>
         </is>
       </c>
       <c r="AX9" s="3" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6B ENGLISH</t>
+          <t>7D ENGLISH</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -2431,7 +2431,7 @@
       <c r="AJ12" s="2" t="inlineStr"/>
       <c r="AK12" s="2" t="inlineStr">
         <is>
-          <t>7D S.ST</t>
+          <t>6B HISTORY</t>
         </is>
       </c>
       <c r="AL12" s="2" t="inlineStr"/>
@@ -2534,7 +2534,11 @@
           <t>7E GENERAL SCIENCE</t>
         </is>
       </c>
-      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>6B GENERAL SCIENCE</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>6D GENERAL SCIENCE</t>
@@ -2577,11 +2581,7 @@
           <t>8B COMPUTER</t>
         </is>
       </c>
-      <c r="AK13" s="3" t="inlineStr">
-        <is>
-          <t>6B HISTORY</t>
-        </is>
-      </c>
+      <c r="AK13" s="3" t="inlineStr"/>
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr">
@@ -2632,11 +2632,7 @@
           <t>10:10-10:50</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7D ENGLISH</t>
-        </is>
-      </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -2719,7 +2715,11 @@
           <t>10A PHYSICS</t>
         </is>
       </c>
-      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>8A GENERAL SCIENCE</t>
+        </is>
+      </c>
       <c r="AF14" s="2" t="inlineStr"/>
       <c r="AG14" s="2" t="inlineStr">
         <is>
@@ -2737,7 +2737,11 @@
           <t>7C COMPUTER</t>
         </is>
       </c>
-      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr">
+        <is>
+          <t>7D S.ST</t>
+        </is>
+      </c>
       <c r="AL14" s="2" t="inlineStr">
         <is>
           <t>8C SINDHI</t>
@@ -2854,11 +2858,7 @@
           <t>6C ENGLISH</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8C ENGLISH</t>
-        </is>
-      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -2941,7 +2941,11 @@
           <t>10E PHYSICS</t>
         </is>
       </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>10A BIOLOGY</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
           <t>10C PHYSICS</t>
@@ -2970,11 +2974,7 @@
       </c>
       <c r="AJ16" s="2" t="inlineStr"/>
       <c r="AK16" s="2" t="inlineStr"/>
-      <c r="AL16" s="2" t="inlineStr">
-        <is>
-          <t>10A SINDHI-X</t>
-        </is>
-      </c>
+      <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr">
         <is>
           <t>8B SINDHI</t>
@@ -3061,11 +3061,7 @@
           <t>6E MATHS</t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>6C MATHS</t>
-        </is>
-      </c>
+      <c r="U17" s="3" t="inlineStr"/>
       <c r="V17" s="3" t="inlineStr">
         <is>
           <t>9A MATHS</t>
@@ -3119,7 +3115,11 @@
           <t>7A COMPUTER</t>
         </is>
       </c>
-      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>6C COMPUTER</t>
+        </is>
+      </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
           <t>10F COMPUTER IX-X</t>
@@ -3186,7 +3186,11 @@
           <t>6D ENGLISH</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6B ENGLISH</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>9A ENGLISH</t>
@@ -3241,7 +3245,11 @@
           <t>8D MATHS</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>6C MATHS</t>
+        </is>
+      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
           <t>8A MATHS</t>
@@ -3254,18 +3262,10 @@
       </c>
       <c r="X18" s="2" t="inlineStr"/>
       <c r="Y18" s="2" t="inlineStr"/>
-      <c r="Z18" s="2" t="inlineStr">
-        <is>
-          <t>6B GENERAL SCIENCE</t>
-        </is>
-      </c>
+      <c r="Z18" s="2" t="inlineStr"/>
       <c r="AA18" s="2" t="inlineStr"/>
       <c r="AB18" s="2" t="inlineStr"/>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>10A BIOLOGY</t>
-        </is>
-      </c>
+      <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr"/>
       <c r="AE18" s="2" t="inlineStr"/>
       <c r="AF18" s="2" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AL18" s="2" t="inlineStr">
         <is>
-          <t>10E SINDHI-X</t>
+          <t>10A SINDHI-X</t>
         </is>
       </c>
       <c r="AM18" s="2" t="inlineStr">
@@ -3308,7 +3308,7 @@
       <c r="AO18" s="2" t="inlineStr"/>
       <c r="AP18" s="2" t="inlineStr">
         <is>
-          <t>6C S.ST</t>
+          <t>10E PAKISTAN STUDIES</t>
         </is>
       </c>
       <c r="AQ18" s="2" t="inlineStr">
@@ -3458,7 +3458,11 @@
         </is>
       </c>
       <c r="AK19" s="3" t="inlineStr"/>
-      <c r="AL19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>10E SINDHI-X</t>
+        </is>
+      </c>
       <c r="AM19" s="3" t="inlineStr"/>
       <c r="AN19" s="3" t="inlineStr">
         <is>
@@ -3466,11 +3470,7 @@
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr"/>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>10E PAKISTAN STUDIES</t>
-        </is>
-      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       <c r="AB21" s="3" t="inlineStr"/>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>9B BIOLOGY</t>
+          <t>10A BIOLOGY</t>
         </is>
       </c>
       <c r="AD21" s="3" t="inlineStr"/>
@@ -3814,7 +3814,7 @@
       <c r="AU21" s="3" t="inlineStr"/>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>10C GAMES</t>
+          <t>9B GAMES</t>
         </is>
       </c>
       <c r="AW21" s="3" t="inlineStr"/>
@@ -3952,7 +3952,11 @@
       <c r="AK22" s="2" t="inlineStr"/>
       <c r="AL22" s="2" t="inlineStr"/>
       <c r="AM22" s="2" t="inlineStr"/>
-      <c r="AN22" s="2" t="inlineStr"/>
+      <c r="AN22" s="2" t="inlineStr">
+        <is>
+          <t>6C SINDHI</t>
+        </is>
+      </c>
       <c r="AO22" s="2" t="inlineStr">
         <is>
           <t>8C GP</t>
@@ -3977,11 +3981,7 @@
       </c>
       <c r="AU22" s="2" t="inlineStr"/>
       <c r="AV22" s="2" t="inlineStr"/>
-      <c r="AW22" s="2" t="inlineStr">
-        <is>
-          <t>6C GAMES</t>
-        </is>
-      </c>
+      <c r="AW22" s="2" t="inlineStr"/>
       <c r="AX22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
@@ -4222,11 +4222,7 @@
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>8C ENGLISH</t>
-        </is>
-      </c>
+      <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
           <t>9A ENGLISH</t>
@@ -4289,7 +4285,11 @@
           <t>8B MATHS</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>7E GENERAL SCIENCE</t>
+        </is>
+      </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
           <t>6B GENERAL SCIENCE</t>
@@ -4340,11 +4340,7 @@
         </is>
       </c>
       <c r="AM25" s="3" t="inlineStr"/>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6C SINDHI</t>
-        </is>
-      </c>
+      <c r="AN25" s="3" t="inlineStr"/>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>8D GP</t>
@@ -4363,7 +4359,7 @@
       <c r="AV25" s="3" t="inlineStr"/>
       <c r="AW25" s="3" t="inlineStr">
         <is>
-          <t>7E GAMES</t>
+          <t>6C GAMES</t>
         </is>
       </c>
       <c r="AX25" s="3" t="inlineStr"/>
@@ -4445,11 +4441,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr"/>
       <c r="X26" s="2" t="inlineStr"/>
-      <c r="Y26" s="2" t="inlineStr">
-        <is>
-          <t>7E GENERAL SCIENCE</t>
-        </is>
-      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr">
         <is>
           <t>6A GENERAL SCIENCE</t>
@@ -4529,7 +4521,11 @@
           <t>9A GAMES</t>
         </is>
       </c>
-      <c r="AW26" s="2" t="inlineStr"/>
+      <c r="AW26" s="2" t="inlineStr">
+        <is>
+          <t>7E GAMES</t>
+        </is>
+      </c>
       <c r="AX26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
@@ -4561,11 +4557,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>10D ENGLISH</t>
-        </is>
-      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
@@ -4635,7 +4627,11 @@
           <t>9C PHYSICS</t>
         </is>
       </c>
-      <c r="AE27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>8A GENERAL SCIENCE</t>
+        </is>
+      </c>
       <c r="AF27" s="3" t="inlineStr"/>
       <c r="AG27" s="3" t="inlineStr">
         <is>
@@ -4662,7 +4658,11 @@
       <c r="AM27" s="3" t="inlineStr"/>
       <c r="AN27" s="3" t="inlineStr"/>
       <c r="AO27" s="3" t="inlineStr"/>
-      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>10D PAKISTAN STUDIES</t>
+        </is>
+      </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
@@ -4700,13 +4700,13 @@
           <t>1:20-2:00</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>7D ENGLISH</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>10E ENGLISH</t>
@@ -4717,7 +4717,11 @@
           <t>9F ENGLISH</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>10D ENGLISH</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
@@ -4826,11 +4830,7 @@
         </is>
       </c>
       <c r="AO28" s="2" t="inlineStr"/>
-      <c r="AP28" s="2" t="inlineStr">
-        <is>
-          <t>10D PAKISTAN STUDIES</t>
-        </is>
-      </c>
+      <c r="AP28" s="2" t="inlineStr"/>
       <c r="AQ28" s="2" t="inlineStr">
         <is>
           <t>8C MATHS</t>
@@ -5117,7 +5117,11 @@
           <t>10B MATHS</t>
         </is>
       </c>
-      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>8D GENERAL SCIENCE</t>
+        </is>
+      </c>
       <c r="Z30" s="2" t="inlineStr"/>
       <c r="AA30" s="2" t="inlineStr"/>
       <c r="AB30" s="2" t="inlineStr">
@@ -5156,11 +5160,7 @@
       <c r="AK30" s="2" t="inlineStr"/>
       <c r="AL30" s="2" t="inlineStr"/>
       <c r="AM30" s="2" t="inlineStr"/>
-      <c r="AN30" s="2" t="inlineStr">
-        <is>
-          <t>8D SINDHI</t>
-        </is>
-      </c>
+      <c r="AN30" s="2" t="inlineStr"/>
       <c r="AO30" s="2" t="inlineStr"/>
       <c r="AP30" s="2" t="inlineStr">
         <is>
@@ -5366,11 +5366,7 @@
           <t>7B ENGLISH</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>8C ENGLISH</t>
-        </is>
-      </c>
+      <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>9A ENGLISH</t>
@@ -5412,7 +5408,11 @@
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr"/>
-      <c r="T32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>8D MATHS</t>
+        </is>
+      </c>
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr"/>
       <c r="W32" s="2" t="inlineStr">
@@ -5425,11 +5425,7 @@
           <t>9E MATHS</t>
         </is>
       </c>
-      <c r="Y32" s="2" t="inlineStr">
-        <is>
-          <t>8D GENERAL SCIENCE</t>
-        </is>
-      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
       <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>8B GENERAL SCIENCE</t>
@@ -5750,7 +5746,11 @@
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>7D ENGLISH</t>
+        </is>
+      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
           <t>10E ENGLISH</t>
@@ -5889,11 +5889,7 @@
       <c r="AT35" s="3" t="inlineStr"/>
       <c r="AU35" s="3" t="inlineStr"/>
       <c r="AV35" s="3" t="inlineStr"/>
-      <c r="AW35" s="3" t="inlineStr">
-        <is>
-          <t>7D GAMES</t>
-        </is>
-      </c>
+      <c r="AW35" s="3" t="inlineStr"/>
       <c r="AX35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
@@ -5995,7 +5991,11 @@
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr"/>
-      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
+          <t>8A GENERAL SCIENCE</t>
+        </is>
+      </c>
       <c r="AF36" s="2" t="inlineStr">
         <is>
           <t>9D CHEMISTRY</t>
@@ -6068,11 +6068,7 @@
           <t>1:15-2:00</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>7D ENGLISH</t>
-        </is>
-      </c>
+      <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr">
         <is>
           <t>6D ENGLISH</t>
@@ -6217,7 +6213,11 @@
       <c r="AT37" s="3" t="inlineStr"/>
       <c r="AU37" s="3" t="inlineStr"/>
       <c r="AV37" s="3" t="inlineStr"/>
-      <c r="AW37" s="3" t="inlineStr"/>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>7D GAMES</t>
+        </is>
+      </c>
       <c r="AX37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
@@ -6460,11 +6460,7 @@
           <t>6D TS</t>
         </is>
       </c>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t>8D MATHS</t>
-        </is>
-      </c>
+      <c r="T39" s="3" t="inlineStr"/>
       <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" s="3" t="inlineStr"/>
       <c r="W39" s="3" t="inlineStr">
@@ -6528,7 +6524,11 @@
           <t>10F SINDHI-X</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr"/>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>8D SINDHI</t>
+        </is>
+      </c>
       <c r="AO39" s="3" t="inlineStr"/>
       <c r="AP39" s="3" t="inlineStr"/>
       <c r="AQ39" s="3" t="inlineStr">
@@ -6564,11 +6564,7 @@
           <t>9:15-9:50</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>7D ENGLISH</t>
-        </is>
-      </c>
+      <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
           <t>7B ENGLISH</t>
@@ -6628,13 +6624,21 @@
           <t>9B MATHS</t>
         </is>
       </c>
-      <c r="T40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>7D MATHS</t>
+        </is>
+      </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
           <t>6A MATHS</t>
         </is>
       </c>
-      <c r="V40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>8A MATHS</t>
+        </is>
+      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
           <t>7E MATHS</t>
@@ -6770,21 +6774,17 @@
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>7D ISLAMIAT</t>
+        </is>
+      </c>
       <c r="O41" s="3" t="inlineStr"/>
       <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>9E ISLAMIAT IX</t>
-        </is>
-      </c>
+      <c r="R41" s="3" t="inlineStr"/>
       <c r="S41" s="3" t="inlineStr"/>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t>7D MATHS</t>
-        </is>
-      </c>
+      <c r="T41" s="3" t="inlineStr"/>
       <c r="U41" s="3" t="inlineStr">
         <is>
           <t>6B MATHS</t>
@@ -6824,18 +6824,18 @@
           <t>9C CHEMISTRY</t>
         </is>
       </c>
-      <c r="AF41" s="3" t="inlineStr"/>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>9E CHEMISTRY</t>
+        </is>
+      </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
           <t>9F GENERAL SCIENCE</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr"/>
-      <c r="AI41" s="3" t="inlineStr">
-        <is>
-          <t>6C COMPUTER</t>
-        </is>
-      </c>
+      <c r="AI41" s="3" t="inlineStr"/>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
           <t>7B COMPUTER</t>
@@ -6858,7 +6858,11 @@
         </is>
       </c>
       <c r="AO41" s="3" t="inlineStr"/>
-      <c r="AP41" s="3" t="inlineStr"/>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>6C S.ST</t>
+        </is>
+      </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
           <t>9D MATHS</t>
@@ -6954,7 +6958,11 @@
           <t>8A ENGLISH</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>7D ENGLISH</t>
+        </is>
+      </c>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr">
@@ -6982,11 +6990,7 @@
           <t>7E URDU</t>
         </is>
       </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t>7D ISLAMIAT</t>
-        </is>
-      </c>
+      <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="3" t="inlineStr"/>
@@ -7114,11 +7118,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>8C ENGLISH</t>
-        </is>
-      </c>
+      <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>9D ENGLISH</t>
@@ -7170,7 +7170,11 @@
           <t>7C ARABIC</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>9E ISLAMIAT IX</t>
+        </is>
+      </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
           <t>7B MATHS</t>
@@ -7182,11 +7186,7 @@
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr"/>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>8A MATHS</t>
-        </is>
-      </c>
+      <c r="V44" s="2" t="inlineStr"/>
       <c r="W44" s="2" t="inlineStr"/>
       <c r="X44" s="2" t="inlineStr"/>
       <c r="Y44" s="2" t="inlineStr">
@@ -7211,7 +7211,11 @@
           <t>9A PHYSICS</t>
         </is>
       </c>
-      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr">
+        <is>
+          <t>8A GENERAL SCIENCE</t>
+        </is>
+      </c>
       <c r="AF44" s="2" t="inlineStr">
         <is>
           <t>9B PHYSICS</t>

--- a/school_timetable.xlsx
+++ b/school_timetable.xlsx
@@ -2852,7 +2852,11 @@
           <t>11:20-12:00</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8C ENGLISH</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>6C ENGLISH</t>
@@ -4347,7 +4351,11 @@
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr"/>
-      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr">
+        <is>
+          <t>8C MATHS</t>
+        </is>
+      </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
           <t>10B PAKISTAN STUDIES</t>
@@ -4700,7 +4708,11 @@
           <t>1:20-2:00</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>8C ENGLISH</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -4831,11 +4843,7 @@
       </c>
       <c r="AO28" s="2" t="inlineStr"/>
       <c r="AP28" s="2" t="inlineStr"/>
-      <c r="AQ28" s="2" t="inlineStr">
-        <is>
-          <t>8C MATHS</t>
-        </is>
-      </c>
+      <c r="AQ28" s="2" t="inlineStr"/>
       <c r="AR28" s="2" t="inlineStr"/>
       <c r="AS28" s="2" t="inlineStr"/>
       <c r="AT28" s="2" t="inlineStr">
@@ -5360,7 +5368,11 @@
           <t>10:40-11:15</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>8C ENGLISH</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t>7B ENGLISH</t>
@@ -6564,7 +6576,11 @@
           <t>9:15-9:50</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>8C ENGLISH</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
           <t>7B ENGLISH</t>
@@ -6602,11 +6618,7 @@
           <t>9D URDU</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>8C ISLAMIAT</t>
-        </is>
-      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
@@ -7154,7 +7166,11 @@
           <t>6B URDU</t>
         </is>
       </c>
-      <c r="N44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>8C ISLAMIAT</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
           <t>7E ISLAMIAT</t>
